--- a/ig/main/CodeSystem-1.2.250.1.213.1.1.4.322.xlsx
+++ b/ig/main/CodeSystem-1.2.250.1.213.1.1.4.322.xlsx
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/ig/main/CodeSystem-1.2.250.1.213.1.1.4.322.xlsx
+++ b/ig/main/CodeSystem-1.2.250.1.213.1.1.4.322.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4946" uniqueCount="3286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4949" uniqueCount="3288">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T11:35:32-00:00</t>
+    <t>2024-07-22T11:59:38-00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -774,7 +774,7 @@
     <t>GEN-092.01.13</t>
   </si>
   <si>
-    <t>Autres accidents domestiques</t>
+    <t>Autre(s) accident(s) domestique(s)</t>
   </si>
   <si>
     <t>GEN-092.01.14</t>
@@ -1494,13 +1494,13 @@
     <t>GEN-146</t>
   </si>
   <si>
-    <t>Gérer ces comptes et ses affaires personnelles</t>
+    <t>Gérer ses comptes et ses affaires personnelles</t>
   </si>
   <si>
     <t>GEN-147</t>
   </si>
   <si>
-    <t>Gérer seul ces traitements</t>
+    <t>Gérer seul ses traitements</t>
   </si>
   <si>
     <t>GEN-148</t>
@@ -1512,13 +1512,13 @@
     <t>GEN-149</t>
   </si>
   <si>
-    <t>Communiquer : proches</t>
+    <t>Communiquer : proches</t>
   </si>
   <si>
     <t>GEN-150</t>
   </si>
   <si>
-    <t>Extérieur (Appel secours, courses)</t>
+    <t>Extérieur (appel secours, courses…)</t>
   </si>
   <si>
     <t>GEN-151</t>
@@ -1674,7 +1674,7 @@
     <t>GEN-190</t>
   </si>
   <si>
-    <t>Revenu insuffisant</t>
+    <t>Revenus insuffisants</t>
   </si>
   <si>
     <t>GEN-191</t>
@@ -2268,13 +2268,13 @@
     <t>GEN-312</t>
   </si>
   <si>
-    <t>&lt;1 fois/semaine</t>
+    <t>&lt; 1 fois/semaine</t>
   </si>
   <si>
     <t>GEN-313</t>
   </si>
   <si>
-    <t>≥ 1fois/semaine</t>
+    <t>≥ 1 fois/semaine</t>
   </si>
   <si>
     <t>GEN-314</t>
@@ -2616,7 +2616,7 @@
     <t>MED-007</t>
   </si>
   <si>
-    <t>Mauvaise qualité de l'impression de la mammographie numérique</t>
+    <t>Mauvaise qualité de l'impression de la mammographie numérique, Réimpression du cliché</t>
   </si>
   <si>
     <t>MED-008</t>
@@ -2688,7 +2688,7 @@
     <t>MED-019</t>
   </si>
   <si>
-    <t>Densité glandulaire</t>
+    <t>Densité mammaire</t>
   </si>
   <si>
     <t>MED-020</t>
@@ -2724,7 +2724,7 @@
     <t>MED-025</t>
   </si>
   <si>
-    <t>Console d'interpretation</t>
+    <t>Console d'interprétation</t>
   </si>
   <si>
     <t>MED-026</t>
@@ -2922,7 +2922,7 @@
     <t>MED-061</t>
   </si>
   <si>
-    <t>Troubles nutritrionnels/difficulté à avoir une alimentation adaptée</t>
+    <t>Troubles nutritionnels / difficulté à avoir une alimentation adaptée</t>
   </si>
   <si>
     <t>MED-062</t>
@@ -3192,7 +3192,7 @@
     <t>MED-116</t>
   </si>
   <si>
-    <t>Suivi rapproché &lt; 2 ans</t>
+    <t>Suivi rapproché (&lt; 2 ans)</t>
   </si>
   <si>
     <t>MED-117</t>
@@ -3438,7 +3438,7 @@
     <t>MED-174</t>
   </si>
   <si>
-    <t>Gestes techniques spécialisés</t>
+    <t>Geste technique spécialisé</t>
   </si>
   <si>
     <t>MED-175</t>
@@ -3486,13 +3486,13 @@
     <t>MED-185</t>
   </si>
   <si>
-    <t>Accidents domestiques depuis le 9ème mois</t>
+    <t>Accident(s) domestique(s) depuis le 9ème mois</t>
   </si>
   <si>
     <t>MED-186</t>
   </si>
   <si>
-    <t>Accident domestique avant le 9ème mois</t>
+    <t>Accident(s) domestique(s) avant le 9ème mois</t>
   </si>
   <si>
     <t>MED-187</t>
@@ -4044,7 +4044,7 @@
     <t>MED-329</t>
   </si>
   <si>
-    <t>Spasticité génante</t>
+    <t>Spasticité gênante</t>
   </si>
   <si>
     <t>MED-330</t>
@@ -4056,31 +4056,31 @@
     <t>MED-331</t>
   </si>
   <si>
-    <t>HLH-QLH</t>
+    <t>HLH - QLH</t>
   </si>
   <si>
     <t>MED-332</t>
   </si>
   <si>
-    <t>Troubles de la déglutition</t>
+    <t>Trouble de la déglutition</t>
   </si>
   <si>
     <t>MED-333</t>
   </si>
   <si>
-    <t>Troubles de l'élimination urinaire</t>
+    <t>Trouble de l'élimination urinaire</t>
   </si>
   <si>
     <t>MED-334</t>
   </si>
   <si>
-    <t>Troubles de l'élimination fécale</t>
+    <t>Trouble de l'élimination fécale</t>
   </si>
   <si>
     <t>MED-335</t>
   </si>
   <si>
-    <t>Troubles de la sexualité</t>
+    <t>Trouble de la sexualité</t>
   </si>
   <si>
     <t>MED-336</t>
@@ -4104,37 +4104,37 @@
     <t>MED-339</t>
   </si>
   <si>
-    <t>GIR 1</t>
+    <t>GIR-1</t>
   </si>
   <si>
     <t>MED-340</t>
   </si>
   <si>
-    <t>GIR 2</t>
+    <t>GIR-2</t>
   </si>
   <si>
     <t>MED-341</t>
   </si>
   <si>
-    <t>GIR 3</t>
+    <t>GIR-3</t>
   </si>
   <si>
     <t>MED-342</t>
   </si>
   <si>
-    <t>GIR 4</t>
+    <t>GIR-4</t>
   </si>
   <si>
     <t>MED-343</t>
   </si>
   <si>
-    <t>GIR 5</t>
+    <t>GIR-5</t>
   </si>
   <si>
     <t>MED-344</t>
   </si>
   <si>
-    <t>GIR 6</t>
+    <t>GIR-6</t>
   </si>
   <si>
     <t>MED-345</t>
@@ -4314,7 +4314,7 @@
     <t>MED-374</t>
   </si>
   <si>
-    <t>Traitement concomitant par des anticoagulants oraux avec INR &amp;gt; 1.7 (AHA 2007)</t>
+    <t>Traitement concomitant par des anticoagulants oraux avec INR &gt; 1.7 (AHA 2007)</t>
   </si>
   <si>
     <t>MED-375</t>
@@ -4518,7 +4518,7 @@
     <t>MED-468</t>
   </si>
   <si>
-    <t>Microsaignments</t>
+    <t>Microsaignements</t>
   </si>
   <si>
     <t>MED-469</t>
@@ -4770,7 +4770,7 @@
     <t>MED-518</t>
   </si>
   <si>
-    <t>Complicatios pulmonaire</t>
+    <t>Complication pulmonaire</t>
   </si>
   <si>
     <t>MED-519</t>
@@ -5016,7 +5016,7 @@
     <t>MED-561</t>
   </si>
   <si>
-    <t>Réajustement des soin(s) de support et accompagnement(s)</t>
+    <t>Réajustement des soins de support et accompagnements</t>
   </si>
   <si>
     <t>MED-562</t>
@@ -5376,7 +5376,7 @@
     <t>MED-625</t>
   </si>
   <si>
-    <t>Grade III : Symptômes menaçant la vie : collapsus, tachycardie ou bradycardie, arythmies,bronchospasme</t>
+    <t>Grade III : Symptômes menaçant la vie : collapsus, tachycardie ou bradycardie, arythmies, bronchospasme</t>
   </si>
   <si>
     <t>MED-626</t>
@@ -7488,7 +7488,7 @@
     <t>MED-1065</t>
   </si>
   <si>
-    <t>Valeur de la Kératométrie Dans l'Axe Le Plus Plat</t>
+    <t>Valeur de la kératométrie dans l'axe le plus plat</t>
   </si>
   <si>
     <t>MED-1066</t>
@@ -7518,37 +7518,37 @@
     <t>MED-1071</t>
   </si>
   <si>
-    <t>Puissance de la sphère – verre prescrit</t>
+    <t>Puissance de la sphère - verre prescrit</t>
   </si>
   <si>
     <t>MED-1072</t>
   </si>
   <si>
-    <t>Puissance du cylindre – verre prescrit</t>
+    <t>Puissance du cylindre - verre prescrit</t>
   </si>
   <si>
     <t>MED-1073</t>
   </si>
   <si>
-    <t>Prisme – puissance – verre prescrit</t>
+    <t>Prisme - puissance - verre prescrit</t>
   </si>
   <si>
     <t>MED-1074</t>
   </si>
   <si>
-    <t>Prisme - orientation base – verre prescrit</t>
+    <t>Prisme - orientation base - verre prescrit</t>
   </si>
   <si>
     <t>MED-1075</t>
   </si>
   <si>
-    <t>Prisme - axe en degrés – verre prescrit</t>
+    <t>Prisme - axe en degrés - verre prescrit</t>
   </si>
   <si>
     <t>MED-1076</t>
   </si>
   <si>
-    <t>Axe en degrés – verre prescrit</t>
+    <t>Axe en degrés - verre prescrit</t>
   </si>
   <si>
     <t>MED-1077</t>
@@ -7758,7 +7758,7 @@
     <t>MED-1111</t>
   </si>
   <si>
-    <t>Patient porteur de clips métalliques ou coils intracrâniens)</t>
+    <t>Patient porteur de clips métalliques ou coils intracrâniens</t>
   </si>
   <si>
     <t>MED-1112</t>
@@ -8190,25 +8190,25 @@
     <t>MED-1188</t>
   </si>
   <si>
-    <t>Vous avez effectué un test de dépistage du cancer du col de l’utérus. Celui-ci est non interprétable. Cela signifie que l’analyse de votre prélèvement est non concluante ou n’a pas pu être effectuée. Nous vous recommandons vivement de consulter votre médecin ou votre sage-femme afin qu’un nouveau prélèvement puisse être refait dans un délai de 3 mois. Pour une bonne coordination, vos résultats sont envoyés aux professionnels de santé concernés par votre dépistage. Ils sont également transmis au médecin coordonnateur du centre de coordination des dépistages des cancers de votre région.</t>
+    <t>Vous avez effectué un test de dépistage dans le cadre du programme de dépistage du cancer du col de l’utérus. Celui-ci est non interprétable. Cela signifie que l’analyse de votre prélèvement est non concluante ou n’a pas pu être effectuée. Nous vous recommandons vivement de consulter votre médecin ou votre sage-femme afin qu’un nouveau prélèvement puisse être refait dans un délai de 3 mois. Pour une bonne coordination, vos résultats sont envoyés aux professionnels de santé concernés par votre dépistage. Ils sont également transmis au médecin coordonnateur du centre de coordination des dépistages des cancers de votre région.</t>
   </si>
   <si>
     <t>MED-1189</t>
   </si>
   <si>
-    <t>Vous avez effectué un test de dépistage du cancer du col de l’utérus. Celui-ci n’a pas révélé d’anomalie. N’oubliez pas de refaire un test de dépistage dans 5 ans. D'ici là, nous vous invitons à consulter votre médecin ou votre sage-femme en cas de troubles ou symptômes (saignements vaginaux anormaux inhabituelles, pertes vaginales anormales, douleurs, etc.).Pour une bonne coordination, vos résultats sont envoyés aux professionnels de santé concernés par votre dépistage. Ils sont également transmis au médecin coordonnateur du centre de coordination des dépistages des cancers de votre région.</t>
+    <t>Vous avez effectué un test de dépistage dans le cadre du programme de dépistage du cancer du col de l’utérus. Celui-ci n’a pas révélé d’anomalie. N’oubliez pas de refaire un test de dépistage dans 5 ans. D'ici là, nous vous invitons à consulter votre médecin ou votre sage-femme en cas de troubles ou symptômes (saignements vaginaux anormaux inhabituelles, pertes vaginales anormales, douleurs, etc.).Pour une bonne coordination, vos résultats sont envoyés aux professionnels de santé concernés par votre dépistage. Ils sont également transmis au médecin coordonnateur du centre de coordination des dépistages des cancers de votre région.</t>
   </si>
   <si>
     <t>MED-1190</t>
   </si>
   <si>
-    <t>Vous avez effectué un test de dépistage du cancer du col de l’utérus.Celui-ci a révélé une anomalie. Cela ne signifie pas que vous avez un cancer mais que des examens complémentaires ou un suivi spécifique peuvent être nécessaires. Nous vous recommandons vivement de contacter votre médecin ou votre sage-femme qui vous expliquera les résultats et vous indiquera le suivi à mettre en place ou les éventuels examens complémentaires à réaliser. Il ou elle vous orientera, si besoin, vers un professionnel de santé spécialisé. Pour une bonne coordination, vos résultats sont envoyés aux professionnels de santé concernés par votre dépistage. Ils sont également transmis au médecin coordonnateur du centre de coordination des dépistages des cancers de votre région.</t>
+    <t>Vous avez effectué un test de dépistage dans le cadre du programme de dépistage du cancer du col de l’utérus.Celui-ci a révélé une anomalie. Cela ne signifie pas que vous avez un cancer mais que des examens complémentaires ou un suivi spécifique peuvent être nécessaires. Nous vous recommandons vivement de contacter votre médecin ou votre sage-femme qui vous expliquera les résultats et vous indiquera le suivi à mettre en place ou les éventuels examens complémentaires à réaliser. Il ou elle vous orientera, si besoin, vers un professionnel de santé spécialisé. Pour une bonne coordination, vos résultats sont envoyés aux professionnels de santé concernés par votre dépistage. Ils sont également transmis au médecin coordonnateur du centre de coordination des dépistages des cancers de votre région.</t>
   </si>
   <si>
     <t>MED-1191</t>
   </si>
   <si>
-    <t>Vous avez effectué un test de dépistage du cancer du col de l’utérus.Celui-ci n’a pas révélé d’anomalie. N’oubliez pas de refaire un test de dépistage dans 3 ans ou dans 1 an si c’est votre premier dépistage. D'ici là, nous vous invitons à consulter votre médecin ou votre sage-femme en cas de troubles ou symptômes (saignements vaginaux anormaux inhabituelles, pertes vaginales anormales, douleurs, etc.). Pour une bonne coordination, vos résultats sont envoyés aux professionnels de santé concernés par votre dépistage. Ils sont également transmis au médecin coordonnateur du centre de coordination des dépistages des cancers de votre région.</t>
+    <t>Vous avez effectué un test de dépistage dans le cadre du programme de dépistage du cancer du col de l’utérus.Celui-ci n’a pas révélé d’anomalie. N’oubliez pas de refaire un test de dépistage dans 3 ans ou dans 1 an si c’est votre premier dépistage. D'ici là, nous vous invitons à consulter votre médecin ou votre sage-femme en cas de troubles ou symptômes (saignements vaginaux anormaux inhabituelles, pertes vaginales anormales, douleurs, etc.). Pour une bonne coordination, vos résultats sont envoyés aux professionnels de santé concernés par votre dépistage. Ils sont également transmis au médecin coordonnateur du centre de coordination des dépistages des cancers de votre région.</t>
   </si>
   <si>
     <t>MED-1192</t>
@@ -8727,6 +8727,12 @@
     <t>décès sans rapport avec l’effet</t>
   </si>
   <si>
+    <t>MED-1283</t>
+  </si>
+  <si>
+    <t>Sans indication médicale</t>
+  </si>
+  <si>
     <t>ORG-001</t>
   </si>
   <si>
@@ -8961,7 +8967,7 @@
     <t>ORG-057</t>
   </si>
   <si>
-    <t>Organisme sociaux et de maintien dans l'emploi</t>
+    <t>Organisme social et de maintien dans l'emploi</t>
   </si>
   <si>
     <t>ORG-059</t>
@@ -9846,7 +9852,7 @@
     <t>PAT-056</t>
   </si>
   <si>
-    <t>Age &lt;18 ans et &gt;80 ans</t>
+    <t>Age &lt; 18 ans et &gt; 80 ans</t>
   </si>
   <si>
     <t>PAT-057</t>
@@ -10184,7 +10190,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1636"/>
+  <dimension ref="A1:D1637"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -27921,7 +27927,7 @@
         <v>2970</v>
       </c>
       <c r="C1478" t="s" s="2">
-        <v>1687</v>
+        <v>2971</v>
       </c>
       <c r="D1478" s="2"/>
     </row>
@@ -27930,10 +27936,10 @@
         <v>40</v>
       </c>
       <c r="B1479" t="s" s="2">
-        <v>2971</v>
+        <v>2972</v>
       </c>
       <c r="C1479" t="s" s="2">
-        <v>2972</v>
+        <v>1687</v>
       </c>
       <c r="D1479" s="2"/>
     </row>
@@ -29013,7 +29019,7 @@
         <v>3151</v>
       </c>
       <c r="C1569" t="s" s="2">
-        <v>2976</v>
+        <v>3152</v>
       </c>
       <c r="D1569" s="2"/>
     </row>
@@ -29022,10 +29028,10 @@
         <v>40</v>
       </c>
       <c r="B1570" t="s" s="2">
-        <v>3152</v>
+        <v>3153</v>
       </c>
       <c r="C1570" t="s" s="2">
-        <v>3153</v>
+        <v>2978</v>
       </c>
       <c r="D1570" s="2"/>
     </row>
@@ -29820,6 +29826,18 @@
         <v>3285</v>
       </c>
       <c r="D1636" s="2"/>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1637" t="s" s="2">
+        <v>3286</v>
+      </c>
+      <c r="C1637" t="s" s="2">
+        <v>3287</v>
+      </c>
+      <c r="D1637" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/ig/main/CodeSystem-1.2.250.1.213.1.1.4.322.xlsx
+++ b/ig/main/CodeSystem-1.2.250.1.213.1.1.4.322.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4949" uniqueCount="3288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5186" uniqueCount="3450">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-22T11:59:38-00:00</t>
+    <t>2024-10-08T14:13:50-00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1098,7 +1098,7 @@
     <t>GEN-092.06</t>
   </si>
   <si>
-    <t>Autre Lieu - Ne pas utiliser</t>
+    <t>Autre Lieu / Transport - Ne pas utiliser</t>
   </si>
   <si>
     <t>GEN-092.06.01</t>
@@ -1149,6 +1149,12 @@
     <t>Autre mode de sortie</t>
   </si>
   <si>
+    <t>GEN-092.06.10</t>
+  </si>
+  <si>
+    <t>Autre ressource</t>
+  </si>
+  <si>
     <t>GEN-092.07</t>
   </si>
   <si>
@@ -1215,24 +1221,24 @@
     <t>Autre milieu</t>
   </si>
   <si>
+    <t>GEN-092.09</t>
+  </si>
+  <si>
+    <t>Autre rencontre - Ne pas utiliser</t>
+  </si>
+  <si>
+    <t>GEN-092.09.01</t>
+  </si>
+  <si>
+    <t>Autre type de rencontre</t>
+  </si>
+  <si>
     <t>GEN-093</t>
   </si>
   <si>
     <t>Si réponse autre</t>
   </si>
   <si>
-    <t>GEN-092.09</t>
-  </si>
-  <si>
-    <t>Autre rencontre - Ne pas utiliser</t>
-  </si>
-  <si>
-    <t>GEN-092.09.01</t>
-  </si>
-  <si>
-    <t>Autre type de rencontre</t>
-  </si>
-  <si>
     <t>GEN-098</t>
   </si>
   <si>
@@ -2019,30 +2025,6 @@
     <t>Nombre</t>
   </si>
   <si>
-    <t>GEN-266</t>
-  </si>
-  <si>
-    <t>Intégré</t>
-  </si>
-  <si>
-    <t>GEN-267</t>
-  </si>
-  <si>
-    <t>Souple</t>
-  </si>
-  <si>
-    <t>GEN-268</t>
-  </si>
-  <si>
-    <t>Rigide</t>
-  </si>
-  <si>
-    <t>GEN-269</t>
-  </si>
-  <si>
-    <t>Hybride</t>
-  </si>
-  <si>
     <t>GEN-273</t>
   </si>
   <si>
@@ -2286,7 +2268,7 @@
     <t>GEN-315</t>
   </si>
   <si>
-    <t>Opposition du patient à l'utilisation de ses données dans le cadre d'analyses de santé publique</t>
+    <t>Le patient (ou son représentant légal) s'oppose à la réutilisation de ses données pour la recherche</t>
   </si>
   <si>
     <t>GEN-316</t>
@@ -2295,12 +2277,6 @@
     <t>Date d'opposition du patient à l'utilisation de ses données dans le cadre d'analyses de santé publique</t>
   </si>
   <si>
-    <t>GEN-317</t>
-  </si>
-  <si>
-    <t>Non-opposition du patient à l'utilisation de ses données dans le cadre d'analyses de santé publique</t>
-  </si>
-  <si>
     <t>GEN-318</t>
   </si>
   <si>
@@ -2313,6 +2289,288 @@
     <t>Evolution de l'effet indésirable</t>
   </si>
   <si>
+    <t>GEN-320</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN EuRREB</t>
+  </si>
+  <si>
+    <t>GEN-321</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN CRANIO</t>
+  </si>
+  <si>
+    <t>GEN-322</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN EpiCARE</t>
+  </si>
+  <si>
+    <t>GEN-323</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN ERKReg</t>
+  </si>
+  <si>
+    <t>GEN-324</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN RND</t>
+  </si>
+  <si>
+    <t>GEN-325</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN EPSA</t>
+  </si>
+  <si>
+    <t>GEN-326</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN LUNG</t>
+  </si>
+  <si>
+    <t>GEN-327</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN ERRAS</t>
+  </si>
+  <si>
+    <t>GEN-328</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN EURACAN</t>
+  </si>
+  <si>
+    <t>GEN-329</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN ENROL</t>
+  </si>
+  <si>
+    <t>GEN-330</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN eUROGEN</t>
+  </si>
+  <si>
+    <t>GEN-331</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN Euro-NMD</t>
+  </si>
+  <si>
+    <t>GEN-332</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN RED</t>
+  </si>
+  <si>
+    <t>GEN-333</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN GENTURIS</t>
+  </si>
+  <si>
+    <t>GEN-334</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN cond-GUARD-HEART</t>
+  </si>
+  <si>
+    <t>GEN-335</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN Heart-Core</t>
+  </si>
+  <si>
+    <t>GEN-336</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN ILIAD</t>
+  </si>
+  <si>
+    <t>GEN-337</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN UIMD</t>
+  </si>
+  <si>
+    <t>GEN-338</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN PaedCan</t>
+  </si>
+  <si>
+    <t>GEN-339</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN R-Liver</t>
+  </si>
+  <si>
+    <t>GEN-340</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN TogethERN</t>
+  </si>
+  <si>
+    <t>GEN-341</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN RITA</t>
+  </si>
+  <si>
+    <t>GEN-342</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN PETER</t>
+  </si>
+  <si>
+    <t>GEN-343</t>
+  </si>
+  <si>
+    <t>Le patient a signé son consentement à la transmission des données au registre ERN VASCERN</t>
+  </si>
+  <si>
+    <t>GEN-344</t>
+  </si>
+  <si>
+    <t>Bio-banque(s)</t>
+  </si>
+  <si>
+    <t>GEN-345</t>
+  </si>
+  <si>
+    <t>Nature du transport</t>
+  </si>
+  <si>
+    <t>GEN-346</t>
+  </si>
+  <si>
+    <t>Type de motorisation</t>
+  </si>
+  <si>
+    <t>GEN-347</t>
+  </si>
+  <si>
+    <t>Evènement hors prestation</t>
+  </si>
+  <si>
+    <t>GEN-348</t>
+  </si>
+  <si>
+    <t>Motif du statut métier</t>
+  </si>
+  <si>
+    <t>GEN-349</t>
+  </si>
+  <si>
+    <t>Type de ressource utilisée</t>
+  </si>
+  <si>
+    <t>GEN-350</t>
+  </si>
+  <si>
+    <t>Repas  inclus</t>
+  </si>
+  <si>
+    <t>GEN-351</t>
+  </si>
+  <si>
+    <t>Établissement ou service social ou médico-social (ESSMS)</t>
+  </si>
+  <si>
+    <t>GEN-352</t>
+  </si>
+  <si>
+    <t>Catégorie d'évènement</t>
+  </si>
+  <si>
+    <t>GEN-353</t>
+  </si>
+  <si>
+    <t>Durée de transport théorique</t>
+  </si>
+  <si>
+    <t>GEN-354</t>
+  </si>
+  <si>
+    <t>Véhicule thermique</t>
+  </si>
+  <si>
+    <t>GEN-355</t>
+  </si>
+  <si>
+    <t>Véhicule électrique</t>
+  </si>
+  <si>
+    <t>GEN-356</t>
+  </si>
+  <si>
+    <t>Véhicule hybride</t>
+  </si>
+  <si>
+    <t>GEN-357</t>
+  </si>
+  <si>
+    <t>Motif lié à la structure</t>
+  </si>
+  <si>
+    <t>GEN-358</t>
+  </si>
+  <si>
+    <t>Motif lié à l'usager</t>
+  </si>
+  <si>
+    <t>GEN-359</t>
+  </si>
+  <si>
+    <t>Motif lié aux professionnels</t>
+  </si>
+  <si>
+    <t>GEN-360</t>
+  </si>
+  <si>
+    <t>Motif lié à des facteurs externes</t>
+  </si>
+  <si>
+    <t>GEN-361</t>
+  </si>
+  <si>
+    <t>Motif administratif ou légal</t>
+  </si>
+  <si>
+    <t>GEN-362</t>
+  </si>
+  <si>
+    <t>Historique des séjours</t>
+  </si>
+  <si>
+    <t>GEN-363</t>
+  </si>
+  <si>
+    <t>Réforme SERAFIN</t>
+  </si>
+  <si>
+    <t>GEN-364</t>
+  </si>
+  <si>
+    <t>Réforme SSIAD</t>
+  </si>
+  <si>
+    <t>GEN-365</t>
+  </si>
+  <si>
+    <t>Aucun de ces motifs</t>
+  </si>
+  <si>
+    <t>GEN-366</t>
+  </si>
+  <si>
+    <t>Le patient (ou son représentant légal) a donné son consentement pour la réalisation du test.</t>
+  </si>
+  <si>
     <t>image/bm</t>
   </si>
   <si>
@@ -7056,6 +7314,18 @@
     <t>Métastases dans le SNC</t>
   </si>
   <si>
+    <t>MED-969</t>
+  </si>
+  <si>
+    <t>Glucose interstitiel</t>
+  </si>
+  <si>
+    <t>MED-972</t>
+  </si>
+  <si>
+    <t>Index de gestion de glycémie (IGG)</t>
+  </si>
+  <si>
     <t>MED-990</t>
   </si>
   <si>
@@ -8358,18 +8628,33 @@
     <t>MED-1216</t>
   </si>
   <si>
+    <t>Prisme intégré</t>
+  </si>
+  <si>
     <t>MED-1217</t>
   </si>
   <si>
+    <t>Prisme souple</t>
+  </si>
+  <si>
     <t>MED-1218</t>
   </si>
   <si>
+    <t>Lentille souple</t>
+  </si>
+  <si>
     <t>MED-1219</t>
   </si>
   <si>
+    <t>Lentille rigide</t>
+  </si>
+  <si>
     <t>MED-1220</t>
   </si>
   <si>
+    <t>Lentille hybride</t>
+  </si>
+  <si>
     <t>MED-1221</t>
   </si>
   <si>
@@ -8733,6 +9018,93 @@
     <t>Sans indication médicale</t>
   </si>
   <si>
+    <t>MED-1284</t>
+  </si>
+  <si>
+    <t>Description clinique</t>
+  </si>
+  <si>
+    <t>MED-1286</t>
+  </si>
+  <si>
+    <t>Technique sur laquelle repose le diagnostic génétique</t>
+  </si>
+  <si>
+    <t>MED-1287</t>
+  </si>
+  <si>
+    <t>MED-1288</t>
+  </si>
+  <si>
+    <t>Aucun signe</t>
+  </si>
+  <si>
+    <t>MED-1289</t>
+  </si>
+  <si>
+    <t>Rendu de résultat diagnostic génétique</t>
+  </si>
+  <si>
+    <t>MED-1290</t>
+  </si>
+  <si>
+    <t>Evaluation de la situation SSIAD</t>
+  </si>
+  <si>
+    <t>MED-1291</t>
+  </si>
+  <si>
+    <t>Evaluation SERAFIN</t>
+  </si>
+  <si>
+    <t>MED-1292</t>
+  </si>
+  <si>
+    <t>Evaluation AGGIR PH SSIAD</t>
+  </si>
+  <si>
+    <t>MED-1293</t>
+  </si>
+  <si>
+    <t>Evaluation AGGIR PA SSIAD</t>
+  </si>
+  <si>
+    <t>MED-1294</t>
+  </si>
+  <si>
+    <t>Soins IDE pour escarres et autres plaies chroniques</t>
+  </si>
+  <si>
+    <t>MED-1295</t>
+  </si>
+  <si>
+    <t>Prise en charge IDE du diabète insulinotraité</t>
+  </si>
+  <si>
+    <t>MED-1296</t>
+  </si>
+  <si>
+    <t>Intervention d'un aide soignant</t>
+  </si>
+  <si>
+    <t>MED-1297</t>
+  </si>
+  <si>
+    <t>Intervention d'un infirmier libéral</t>
+  </si>
+  <si>
+    <t>MED-1298</t>
+  </si>
+  <si>
+    <t>Intervention d'un infirmer salarié</t>
+  </si>
+  <si>
+    <t>MED-1299</t>
+  </si>
+  <si>
+    <t>Intervention conjointe</t>
+  </si>
+  <si>
     <t>ORG-001</t>
   </si>
   <si>
@@ -9591,6 +9963,90 @@
     <t>Orientation vers une plateforme de coordination et d'orientation</t>
   </si>
   <si>
+    <t>ORG-198</t>
+  </si>
+  <si>
+    <t>RCP régionale ou locale - centre organisateur</t>
+  </si>
+  <si>
+    <t>ORG-199</t>
+  </si>
+  <si>
+    <t>RCP nationale ou européenne - centre participatif</t>
+  </si>
+  <si>
+    <t>ORG-200</t>
+  </si>
+  <si>
+    <t>Budget réel</t>
+  </si>
+  <si>
+    <t>ORG-201</t>
+  </si>
+  <si>
+    <t>Budget prévisionnel</t>
+  </si>
+  <si>
+    <t>ORG-202</t>
+  </si>
+  <si>
+    <t>Véhicule individuel</t>
+  </si>
+  <si>
+    <t>ORG-203</t>
+  </si>
+  <si>
+    <t>Véhicule collectif</t>
+  </si>
+  <si>
+    <t>ORG-204</t>
+  </si>
+  <si>
+    <t>Transport en commun</t>
+  </si>
+  <si>
+    <t>ORG-205</t>
+  </si>
+  <si>
+    <t>Modes doux</t>
+  </si>
+  <si>
+    <t>ORG-206</t>
+  </si>
+  <si>
+    <t>Matériel spécialisé</t>
+  </si>
+  <si>
+    <t>ORG-207</t>
+  </si>
+  <si>
+    <t>Ressource immobilière</t>
+  </si>
+  <si>
+    <t>ORG-208</t>
+  </si>
+  <si>
+    <t>Materiel médical</t>
+  </si>
+  <si>
+    <t>ORG-209</t>
+  </si>
+  <si>
+    <t>Matériel pédagogique</t>
+  </si>
+  <si>
+    <t>ORG-210</t>
+  </si>
+  <si>
+    <t>Salle</t>
+  </si>
+  <si>
+    <t>ORG-211</t>
+  </si>
+  <si>
+    <t>Chambre</t>
+  </si>
+  <si>
     <t>PAT-001</t>
   </si>
   <si>
@@ -9666,7 +10122,7 @@
     <t>PAT-013</t>
   </si>
   <si>
-    <t>Age aux premiers signes</t>
+    <t>Période des premiers signes</t>
   </si>
   <si>
     <t>PAT-014</t>
@@ -9877,6 +10333,36 @@
   </si>
   <si>
     <t>Durée de l'alimentation mixte (à partir de la naissance)</t>
+  </si>
+  <si>
+    <t>PAT-061</t>
+  </si>
+  <si>
+    <t>Patient perdu de vue</t>
+  </si>
+  <si>
+    <t>PAT-062</t>
+  </si>
+  <si>
+    <t>Période du diagnostic clinique</t>
+  </si>
+  <si>
+    <t>PAT-063</t>
+  </si>
+  <si>
+    <t>Précision de l'âge au diagnostic clinique</t>
+  </si>
+  <si>
+    <t>PAT-064</t>
+  </si>
+  <si>
+    <t>Période du diagnostic génétique</t>
+  </si>
+  <si>
+    <t>PAT-065</t>
+  </si>
+  <si>
+    <t>Précision de l'âge au diagnostic génétique</t>
   </si>
 </sst>
 </file>
@@ -10190,7 +10676,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1637"/>
+  <dimension ref="A1:D1716"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -21975,7 +22461,7 @@
         <v>2000</v>
       </c>
       <c r="C982" t="s" s="2">
-        <v>1879</v>
+        <v>2001</v>
       </c>
       <c r="D982" s="2"/>
     </row>
@@ -21984,10 +22470,10 @@
         <v>40</v>
       </c>
       <c r="B983" t="s" s="2">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="C983" t="s" s="2">
-        <v>1881</v>
+        <v>2003</v>
       </c>
       <c r="D983" s="2"/>
     </row>
@@ -21996,10 +22482,10 @@
         <v>40</v>
       </c>
       <c r="B984" t="s" s="2">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="C984" t="s" s="2">
-        <v>1883</v>
+        <v>2005</v>
       </c>
       <c r="D984" s="2"/>
     </row>
@@ -22008,10 +22494,10 @@
         <v>40</v>
       </c>
       <c r="B985" t="s" s="2">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="C985" t="s" s="2">
-        <v>1885</v>
+        <v>2007</v>
       </c>
       <c r="D985" s="2"/>
     </row>
@@ -22020,10 +22506,10 @@
         <v>40</v>
       </c>
       <c r="B986" t="s" s="2">
-        <v>2004</v>
+        <v>2008</v>
       </c>
       <c r="C986" t="s" s="2">
-        <v>1887</v>
+        <v>2009</v>
       </c>
       <c r="D986" s="2"/>
     </row>
@@ -22032,10 +22518,10 @@
         <v>40</v>
       </c>
       <c r="B987" t="s" s="2">
-        <v>2005</v>
+        <v>2010</v>
       </c>
       <c r="C987" t="s" s="2">
-        <v>1889</v>
+        <v>2011</v>
       </c>
       <c r="D987" s="2"/>
     </row>
@@ -22044,10 +22530,10 @@
         <v>40</v>
       </c>
       <c r="B988" t="s" s="2">
-        <v>2006</v>
+        <v>2012</v>
       </c>
       <c r="C988" t="s" s="2">
-        <v>1891</v>
+        <v>2013</v>
       </c>
       <c r="D988" s="2"/>
     </row>
@@ -22056,10 +22542,10 @@
         <v>40</v>
       </c>
       <c r="B989" t="s" s="2">
-        <v>2007</v>
+        <v>2014</v>
       </c>
       <c r="C989" t="s" s="2">
-        <v>1893</v>
+        <v>2015</v>
       </c>
       <c r="D989" s="2"/>
     </row>
@@ -22068,10 +22554,10 @@
         <v>40</v>
       </c>
       <c r="B990" t="s" s="2">
-        <v>2008</v>
+        <v>2016</v>
       </c>
       <c r="C990" t="s" s="2">
-        <v>2009</v>
+        <v>2017</v>
       </c>
       <c r="D990" s="2"/>
     </row>
@@ -22080,10 +22566,10 @@
         <v>40</v>
       </c>
       <c r="B991" t="s" s="2">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="C991" t="s" s="2">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="D991" s="2"/>
     </row>
@@ -22092,10 +22578,10 @@
         <v>40</v>
       </c>
       <c r="B992" t="s" s="2">
-        <v>2012</v>
+        <v>2020</v>
       </c>
       <c r="C992" t="s" s="2">
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="D992" s="2"/>
     </row>
@@ -22104,10 +22590,10 @@
         <v>40</v>
       </c>
       <c r="B993" t="s" s="2">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="C993" t="s" s="2">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="D993" s="2"/>
     </row>
@@ -22116,10 +22602,10 @@
         <v>40</v>
       </c>
       <c r="B994" t="s" s="2">
-        <v>2016</v>
+        <v>2024</v>
       </c>
       <c r="C994" t="s" s="2">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="D994" s="2"/>
     </row>
@@ -22128,10 +22614,10 @@
         <v>40</v>
       </c>
       <c r="B995" t="s" s="2">
-        <v>2018</v>
+        <v>2026</v>
       </c>
       <c r="C995" t="s" s="2">
-        <v>2019</v>
+        <v>2027</v>
       </c>
       <c r="D995" s="2"/>
     </row>
@@ -22140,10 +22626,10 @@
         <v>40</v>
       </c>
       <c r="B996" t="s" s="2">
-        <v>2020</v>
+        <v>2028</v>
       </c>
       <c r="C996" t="s" s="2">
-        <v>2021</v>
+        <v>2029</v>
       </c>
       <c r="D996" s="2"/>
     </row>
@@ -22152,10 +22638,10 @@
         <v>40</v>
       </c>
       <c r="B997" t="s" s="2">
-        <v>2022</v>
+        <v>2030</v>
       </c>
       <c r="C997" t="s" s="2">
-        <v>2023</v>
+        <v>2031</v>
       </c>
       <c r="D997" s="2"/>
     </row>
@@ -22164,10 +22650,10 @@
         <v>40</v>
       </c>
       <c r="B998" t="s" s="2">
-        <v>2024</v>
+        <v>2032</v>
       </c>
       <c r="C998" t="s" s="2">
-        <v>2025</v>
+        <v>2033</v>
       </c>
       <c r="D998" s="2"/>
     </row>
@@ -22176,10 +22662,10 @@
         <v>40</v>
       </c>
       <c r="B999" t="s" s="2">
-        <v>2026</v>
+        <v>2034</v>
       </c>
       <c r="C999" t="s" s="2">
-        <v>2027</v>
+        <v>2035</v>
       </c>
       <c r="D999" s="2"/>
     </row>
@@ -22188,10 +22674,10 @@
         <v>40</v>
       </c>
       <c r="B1000" t="s" s="2">
-        <v>2028</v>
+        <v>2036</v>
       </c>
       <c r="C1000" t="s" s="2">
-        <v>2029</v>
+        <v>2037</v>
       </c>
       <c r="D1000" s="2"/>
     </row>
@@ -22200,10 +22686,10 @@
         <v>40</v>
       </c>
       <c r="B1001" t="s" s="2">
-        <v>2030</v>
+        <v>2038</v>
       </c>
       <c r="C1001" t="s" s="2">
-        <v>657</v>
+        <v>2039</v>
       </c>
       <c r="D1001" s="2"/>
     </row>
@@ -22212,10 +22698,10 @@
         <v>40</v>
       </c>
       <c r="B1002" t="s" s="2">
-        <v>2031</v>
+        <v>2040</v>
       </c>
       <c r="C1002" t="s" s="2">
-        <v>659</v>
+        <v>2041</v>
       </c>
       <c r="D1002" s="2"/>
     </row>
@@ -22224,10 +22710,10 @@
         <v>40</v>
       </c>
       <c r="B1003" t="s" s="2">
-        <v>2032</v>
+        <v>2042</v>
       </c>
       <c r="C1003" t="s" s="2">
-        <v>2033</v>
+        <v>2043</v>
       </c>
       <c r="D1003" s="2"/>
     </row>
@@ -22236,10 +22722,10 @@
         <v>40</v>
       </c>
       <c r="B1004" t="s" s="2">
-        <v>2034</v>
+        <v>2044</v>
       </c>
       <c r="C1004" t="s" s="2">
-        <v>2035</v>
+        <v>2045</v>
       </c>
       <c r="D1004" s="2"/>
     </row>
@@ -22248,10 +22734,10 @@
         <v>40</v>
       </c>
       <c r="B1005" t="s" s="2">
-        <v>2036</v>
+        <v>2046</v>
       </c>
       <c r="C1005" t="s" s="2">
-        <v>2037</v>
+        <v>2047</v>
       </c>
       <c r="D1005" s="2"/>
     </row>
@@ -22260,10 +22746,10 @@
         <v>40</v>
       </c>
       <c r="B1006" t="s" s="2">
-        <v>2038</v>
+        <v>2048</v>
       </c>
       <c r="C1006" t="s" s="2">
-        <v>2039</v>
+        <v>2049</v>
       </c>
       <c r="D1006" s="2"/>
     </row>
@@ -22272,10 +22758,10 @@
         <v>40</v>
       </c>
       <c r="B1007" t="s" s="2">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="C1007" t="s" s="2">
-        <v>2041</v>
+        <v>2051</v>
       </c>
       <c r="D1007" s="2"/>
     </row>
@@ -22284,10 +22770,10 @@
         <v>40</v>
       </c>
       <c r="B1008" t="s" s="2">
-        <v>2042</v>
+        <v>2052</v>
       </c>
       <c r="C1008" t="s" s="2">
-        <v>2043</v>
+        <v>2053</v>
       </c>
       <c r="D1008" s="2"/>
     </row>
@@ -22296,10 +22782,10 @@
         <v>40</v>
       </c>
       <c r="B1009" t="s" s="2">
-        <v>2044</v>
+        <v>2054</v>
       </c>
       <c r="C1009" t="s" s="2">
-        <v>2045</v>
+        <v>2055</v>
       </c>
       <c r="D1009" s="2"/>
     </row>
@@ -22308,10 +22794,10 @@
         <v>40</v>
       </c>
       <c r="B1010" t="s" s="2">
-        <v>2046</v>
+        <v>2056</v>
       </c>
       <c r="C1010" t="s" s="2">
-        <v>2047</v>
+        <v>2057</v>
       </c>
       <c r="D1010" s="2"/>
     </row>
@@ -22320,10 +22806,10 @@
         <v>40</v>
       </c>
       <c r="B1011" t="s" s="2">
-        <v>2048</v>
+        <v>2058</v>
       </c>
       <c r="C1011" t="s" s="2">
-        <v>2049</v>
+        <v>2059</v>
       </c>
       <c r="D1011" s="2"/>
     </row>
@@ -22332,10 +22818,10 @@
         <v>40</v>
       </c>
       <c r="B1012" t="s" s="2">
-        <v>2050</v>
+        <v>2060</v>
       </c>
       <c r="C1012" t="s" s="2">
-        <v>2051</v>
+        <v>2061</v>
       </c>
       <c r="D1012" s="2"/>
     </row>
@@ -22344,10 +22830,10 @@
         <v>40</v>
       </c>
       <c r="B1013" t="s" s="2">
-        <v>2052</v>
+        <v>2062</v>
       </c>
       <c r="C1013" t="s" s="2">
-        <v>2053</v>
+        <v>2063</v>
       </c>
       <c r="D1013" s="2"/>
     </row>
@@ -22356,10 +22842,10 @@
         <v>40</v>
       </c>
       <c r="B1014" t="s" s="2">
-        <v>2054</v>
+        <v>2064</v>
       </c>
       <c r="C1014" t="s" s="2">
-        <v>2055</v>
+        <v>2065</v>
       </c>
       <c r="D1014" s="2"/>
     </row>
@@ -22368,10 +22854,10 @@
         <v>40</v>
       </c>
       <c r="B1015" t="s" s="2">
-        <v>2056</v>
+        <v>2066</v>
       </c>
       <c r="C1015" t="s" s="2">
-        <v>2057</v>
+        <v>2067</v>
       </c>
       <c r="D1015" s="2"/>
     </row>
@@ -22380,10 +22866,10 @@
         <v>40</v>
       </c>
       <c r="B1016" t="s" s="2">
-        <v>2058</v>
+        <v>2068</v>
       </c>
       <c r="C1016" t="s" s="2">
-        <v>2059</v>
+        <v>2069</v>
       </c>
       <c r="D1016" s="2"/>
     </row>
@@ -22392,10 +22878,10 @@
         <v>40</v>
       </c>
       <c r="B1017" t="s" s="2">
-        <v>2060</v>
+        <v>2070</v>
       </c>
       <c r="C1017" t="s" s="2">
-        <v>2061</v>
+        <v>2071</v>
       </c>
       <c r="D1017" s="2"/>
     </row>
@@ -22404,10 +22890,10 @@
         <v>40</v>
       </c>
       <c r="B1018" t="s" s="2">
-        <v>2062</v>
+        <v>2072</v>
       </c>
       <c r="C1018" t="s" s="2">
-        <v>2063</v>
+        <v>2073</v>
       </c>
       <c r="D1018" s="2"/>
     </row>
@@ -22416,10 +22902,10 @@
         <v>40</v>
       </c>
       <c r="B1019" t="s" s="2">
-        <v>2064</v>
+        <v>2074</v>
       </c>
       <c r="C1019" t="s" s="2">
-        <v>2065</v>
+        <v>2075</v>
       </c>
       <c r="D1019" s="2"/>
     </row>
@@ -22428,10 +22914,10 @@
         <v>40</v>
       </c>
       <c r="B1020" t="s" s="2">
-        <v>2066</v>
+        <v>2076</v>
       </c>
       <c r="C1020" t="s" s="2">
-        <v>2067</v>
+        <v>2077</v>
       </c>
       <c r="D1020" s="2"/>
     </row>
@@ -22440,10 +22926,10 @@
         <v>40</v>
       </c>
       <c r="B1021" t="s" s="2">
-        <v>2068</v>
+        <v>2078</v>
       </c>
       <c r="C1021" t="s" s="2">
-        <v>2069</v>
+        <v>2079</v>
       </c>
       <c r="D1021" s="2"/>
     </row>
@@ -22452,10 +22938,10 @@
         <v>40</v>
       </c>
       <c r="B1022" t="s" s="2">
-        <v>2070</v>
+        <v>2080</v>
       </c>
       <c r="C1022" t="s" s="2">
-        <v>2071</v>
+        <v>2081</v>
       </c>
       <c r="D1022" s="2"/>
     </row>
@@ -22464,10 +22950,10 @@
         <v>40</v>
       </c>
       <c r="B1023" t="s" s="2">
-        <v>2072</v>
+        <v>2082</v>
       </c>
       <c r="C1023" t="s" s="2">
-        <v>2073</v>
+        <v>2083</v>
       </c>
       <c r="D1023" s="2"/>
     </row>
@@ -22476,10 +22962,10 @@
         <v>40</v>
       </c>
       <c r="B1024" t="s" s="2">
-        <v>2074</v>
+        <v>2084</v>
       </c>
       <c r="C1024" t="s" s="2">
-        <v>2075</v>
+        <v>2085</v>
       </c>
       <c r="D1024" s="2"/>
     </row>
@@ -22488,10 +22974,10 @@
         <v>40</v>
       </c>
       <c r="B1025" t="s" s="2">
-        <v>2076</v>
+        <v>2086</v>
       </c>
       <c r="C1025" t="s" s="2">
-        <v>2077</v>
+        <v>1965</v>
       </c>
       <c r="D1025" s="2"/>
     </row>
@@ -22500,10 +22986,10 @@
         <v>40</v>
       </c>
       <c r="B1026" t="s" s="2">
-        <v>2078</v>
+        <v>2087</v>
       </c>
       <c r="C1026" t="s" s="2">
-        <v>2079</v>
+        <v>1967</v>
       </c>
       <c r="D1026" s="2"/>
     </row>
@@ -22512,10 +22998,10 @@
         <v>40</v>
       </c>
       <c r="B1027" t="s" s="2">
-        <v>2080</v>
+        <v>2088</v>
       </c>
       <c r="C1027" t="s" s="2">
-        <v>2081</v>
+        <v>1969</v>
       </c>
       <c r="D1027" s="2"/>
     </row>
@@ -22524,10 +23010,10 @@
         <v>40</v>
       </c>
       <c r="B1028" t="s" s="2">
-        <v>2082</v>
+        <v>2089</v>
       </c>
       <c r="C1028" t="s" s="2">
-        <v>2083</v>
+        <v>1971</v>
       </c>
       <c r="D1028" s="2"/>
     </row>
@@ -22536,10 +23022,10 @@
         <v>40</v>
       </c>
       <c r="B1029" t="s" s="2">
-        <v>2084</v>
+        <v>2090</v>
       </c>
       <c r="C1029" t="s" s="2">
-        <v>2085</v>
+        <v>1973</v>
       </c>
       <c r="D1029" s="2"/>
     </row>
@@ -22548,10 +23034,10 @@
         <v>40</v>
       </c>
       <c r="B1030" t="s" s="2">
-        <v>2086</v>
+        <v>2091</v>
       </c>
       <c r="C1030" t="s" s="2">
-        <v>2087</v>
+        <v>1975</v>
       </c>
       <c r="D1030" s="2"/>
     </row>
@@ -22560,10 +23046,10 @@
         <v>40</v>
       </c>
       <c r="B1031" t="s" s="2">
-        <v>2088</v>
+        <v>2092</v>
       </c>
       <c r="C1031" t="s" s="2">
-        <v>2089</v>
+        <v>1977</v>
       </c>
       <c r="D1031" s="2"/>
     </row>
@@ -22572,10 +23058,10 @@
         <v>40</v>
       </c>
       <c r="B1032" t="s" s="2">
-        <v>2090</v>
+        <v>2093</v>
       </c>
       <c r="C1032" t="s" s="2">
-        <v>2091</v>
+        <v>1979</v>
       </c>
       <c r="D1032" s="2"/>
     </row>
@@ -22584,10 +23070,10 @@
         <v>40</v>
       </c>
       <c r="B1033" t="s" s="2">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="C1033" t="s" s="2">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="D1033" s="2"/>
     </row>
@@ -22596,10 +23082,10 @@
         <v>40</v>
       </c>
       <c r="B1034" t="s" s="2">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="C1034" t="s" s="2">
-        <v>2095</v>
+        <v>2097</v>
       </c>
       <c r="D1034" s="2"/>
     </row>
@@ -22608,10 +23094,10 @@
         <v>40</v>
       </c>
       <c r="B1035" t="s" s="2">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="C1035" t="s" s="2">
-        <v>2097</v>
+        <v>2099</v>
       </c>
       <c r="D1035" s="2"/>
     </row>
@@ -22620,10 +23106,10 @@
         <v>40</v>
       </c>
       <c r="B1036" t="s" s="2">
-        <v>2098</v>
+        <v>2100</v>
       </c>
       <c r="C1036" t="s" s="2">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="D1036" s="2"/>
     </row>
@@ -22632,10 +23118,10 @@
         <v>40</v>
       </c>
       <c r="B1037" t="s" s="2">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="C1037" t="s" s="2">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="D1037" s="2"/>
     </row>
@@ -22644,10 +23130,10 @@
         <v>40</v>
       </c>
       <c r="B1038" t="s" s="2">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="C1038" t="s" s="2">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="D1038" s="2"/>
     </row>
@@ -22656,10 +23142,10 @@
         <v>40</v>
       </c>
       <c r="B1039" t="s" s="2">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="C1039" t="s" s="2">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="D1039" s="2"/>
     </row>
@@ -22668,10 +23154,10 @@
         <v>40</v>
       </c>
       <c r="B1040" t="s" s="2">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="C1040" t="s" s="2">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="D1040" s="2"/>
     </row>
@@ -22680,10 +23166,10 @@
         <v>40</v>
       </c>
       <c r="B1041" t="s" s="2">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="C1041" t="s" s="2">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="D1041" s="2"/>
     </row>
@@ -22692,10 +23178,10 @@
         <v>40</v>
       </c>
       <c r="B1042" t="s" s="2">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="C1042" t="s" s="2">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="D1042" s="2"/>
     </row>
@@ -22704,10 +23190,10 @@
         <v>40</v>
       </c>
       <c r="B1043" t="s" s="2">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="C1043" t="s" s="2">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="D1043" s="2"/>
     </row>
@@ -22716,10 +23202,10 @@
         <v>40</v>
       </c>
       <c r="B1044" t="s" s="2">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="C1044" t="s" s="2">
-        <v>2115</v>
+        <v>659</v>
       </c>
       <c r="D1044" s="2"/>
     </row>
@@ -22728,10 +23214,10 @@
         <v>40</v>
       </c>
       <c r="B1045" t="s" s="2">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="C1045" t="s" s="2">
-        <v>2117</v>
+        <v>661</v>
       </c>
       <c r="D1045" s="2"/>
     </row>
@@ -22767,7 +23253,7 @@
         <v>2122</v>
       </c>
       <c r="C1048" t="s" s="2">
-        <v>2077</v>
+        <v>2123</v>
       </c>
       <c r="D1048" s="2"/>
     </row>
@@ -22776,10 +23262,10 @@
         <v>40</v>
       </c>
       <c r="B1049" t="s" s="2">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="C1049" t="s" s="2">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="D1049" s="2"/>
     </row>
@@ -22788,10 +23274,10 @@
         <v>40</v>
       </c>
       <c r="B1050" t="s" s="2">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="C1050" t="s" s="2">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="D1050" s="2"/>
     </row>
@@ -22800,10 +23286,10 @@
         <v>40</v>
       </c>
       <c r="B1051" t="s" s="2">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="C1051" t="s" s="2">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="D1051" s="2"/>
     </row>
@@ -22812,10 +23298,10 @@
         <v>40</v>
       </c>
       <c r="B1052" t="s" s="2">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="C1052" t="s" s="2">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="D1052" s="2"/>
     </row>
@@ -22824,10 +23310,10 @@
         <v>40</v>
       </c>
       <c r="B1053" t="s" s="2">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="C1053" t="s" s="2">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="D1053" s="2"/>
     </row>
@@ -22836,10 +23322,10 @@
         <v>40</v>
       </c>
       <c r="B1054" t="s" s="2">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="C1054" t="s" s="2">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="D1054" s="2"/>
     </row>
@@ -22848,10 +23334,10 @@
         <v>40</v>
       </c>
       <c r="B1055" t="s" s="2">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="C1055" t="s" s="2">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="D1055" s="2"/>
     </row>
@@ -22860,10 +23346,10 @@
         <v>40</v>
       </c>
       <c r="B1056" t="s" s="2">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="C1056" t="s" s="2">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="D1056" s="2"/>
     </row>
@@ -22872,10 +23358,10 @@
         <v>40</v>
       </c>
       <c r="B1057" t="s" s="2">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="C1057" t="s" s="2">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="D1057" s="2"/>
     </row>
@@ -22884,10 +23370,10 @@
         <v>40</v>
       </c>
       <c r="B1058" t="s" s="2">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="C1058" t="s" s="2">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="D1058" s="2"/>
     </row>
@@ -22896,10 +23382,10 @@
         <v>40</v>
       </c>
       <c r="B1059" t="s" s="2">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="C1059" t="s" s="2">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="D1059" s="2"/>
     </row>
@@ -22908,10 +23394,10 @@
         <v>40</v>
       </c>
       <c r="B1060" t="s" s="2">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="C1060" t="s" s="2">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="D1060" s="2"/>
     </row>
@@ -22920,10 +23406,10 @@
         <v>40</v>
       </c>
       <c r="B1061" t="s" s="2">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="C1061" t="s" s="2">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="D1061" s="2"/>
     </row>
@@ -22932,10 +23418,10 @@
         <v>40</v>
       </c>
       <c r="B1062" t="s" s="2">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="C1062" t="s" s="2">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="D1062" s="2"/>
     </row>
@@ -22944,10 +23430,10 @@
         <v>40</v>
       </c>
       <c r="B1063" t="s" s="2">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="C1063" t="s" s="2">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="D1063" s="2"/>
     </row>
@@ -22956,10 +23442,10 @@
         <v>40</v>
       </c>
       <c r="B1064" t="s" s="2">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="C1064" t="s" s="2">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="D1064" s="2"/>
     </row>
@@ -22968,10 +23454,10 @@
         <v>40</v>
       </c>
       <c r="B1065" t="s" s="2">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="C1065" t="s" s="2">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="D1065" s="2"/>
     </row>
@@ -22980,10 +23466,10 @@
         <v>40</v>
       </c>
       <c r="B1066" t="s" s="2">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="C1066" t="s" s="2">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="D1066" s="2"/>
     </row>
@@ -22992,10 +23478,10 @@
         <v>40</v>
       </c>
       <c r="B1067" t="s" s="2">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="C1067" t="s" s="2">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="D1067" s="2"/>
     </row>
@@ -23004,10 +23490,10 @@
         <v>40</v>
       </c>
       <c r="B1068" t="s" s="2">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="C1068" t="s" s="2">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="D1068" s="2"/>
     </row>
@@ -23016,10 +23502,10 @@
         <v>40</v>
       </c>
       <c r="B1069" t="s" s="2">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="C1069" t="s" s="2">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="D1069" s="2"/>
     </row>
@@ -23028,10 +23514,10 @@
         <v>40</v>
       </c>
       <c r="B1070" t="s" s="2">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="C1070" t="s" s="2">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="D1070" s="2"/>
     </row>
@@ -23040,10 +23526,10 @@
         <v>40</v>
       </c>
       <c r="B1071" t="s" s="2">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="C1071" t="s" s="2">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="D1071" s="2"/>
     </row>
@@ -23052,10 +23538,10 @@
         <v>40</v>
       </c>
       <c r="B1072" t="s" s="2">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="C1072" t="s" s="2">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="D1072" s="2"/>
     </row>
@@ -23064,10 +23550,10 @@
         <v>40</v>
       </c>
       <c r="B1073" t="s" s="2">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="C1073" t="s" s="2">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="D1073" s="2"/>
     </row>
@@ -23076,10 +23562,10 @@
         <v>40</v>
       </c>
       <c r="B1074" t="s" s="2">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="C1074" t="s" s="2">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="D1074" s="2"/>
     </row>
@@ -23088,10 +23574,10 @@
         <v>40</v>
       </c>
       <c r="B1075" t="s" s="2">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="C1075" t="s" s="2">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="D1075" s="2"/>
     </row>
@@ -23100,10 +23586,10 @@
         <v>40</v>
       </c>
       <c r="B1076" t="s" s="2">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="C1076" t="s" s="2">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="D1076" s="2"/>
     </row>
@@ -23112,10 +23598,10 @@
         <v>40</v>
       </c>
       <c r="B1077" t="s" s="2">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="C1077" t="s" s="2">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="D1077" s="2"/>
     </row>
@@ -23124,10 +23610,10 @@
         <v>40</v>
       </c>
       <c r="B1078" t="s" s="2">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="C1078" t="s" s="2">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="D1078" s="2"/>
     </row>
@@ -23136,10 +23622,10 @@
         <v>40</v>
       </c>
       <c r="B1079" t="s" s="2">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="C1079" t="s" s="2">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="D1079" s="2"/>
     </row>
@@ -23148,10 +23634,10 @@
         <v>40</v>
       </c>
       <c r="B1080" t="s" s="2">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="C1080" t="s" s="2">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="D1080" s="2"/>
     </row>
@@ -23160,10 +23646,10 @@
         <v>40</v>
       </c>
       <c r="B1081" t="s" s="2">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="C1081" t="s" s="2">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="D1081" s="2"/>
     </row>
@@ -23172,10 +23658,10 @@
         <v>40</v>
       </c>
       <c r="B1082" t="s" s="2">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="C1082" t="s" s="2">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="D1082" s="2"/>
     </row>
@@ -23184,10 +23670,10 @@
         <v>40</v>
       </c>
       <c r="B1083" t="s" s="2">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="C1083" t="s" s="2">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="D1083" s="2"/>
     </row>
@@ -23196,10 +23682,10 @@
         <v>40</v>
       </c>
       <c r="B1084" t="s" s="2">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="C1084" t="s" s="2">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="D1084" s="2"/>
     </row>
@@ -23208,10 +23694,10 @@
         <v>40</v>
       </c>
       <c r="B1085" t="s" s="2">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="C1085" t="s" s="2">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="D1085" s="2"/>
     </row>
@@ -23220,10 +23706,10 @@
         <v>40</v>
       </c>
       <c r="B1086" t="s" s="2">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="C1086" t="s" s="2">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="D1086" s="2"/>
     </row>
@@ -23232,10 +23718,10 @@
         <v>40</v>
       </c>
       <c r="B1087" t="s" s="2">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="C1087" t="s" s="2">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="D1087" s="2"/>
     </row>
@@ -23244,10 +23730,10 @@
         <v>40</v>
       </c>
       <c r="B1088" t="s" s="2">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="C1088" t="s" s="2">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="D1088" s="2"/>
     </row>
@@ -23256,10 +23742,10 @@
         <v>40</v>
       </c>
       <c r="B1089" t="s" s="2">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="C1089" t="s" s="2">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="D1089" s="2"/>
     </row>
@@ -23268,10 +23754,10 @@
         <v>40</v>
       </c>
       <c r="B1090" t="s" s="2">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="C1090" t="s" s="2">
-        <v>2055</v>
+        <v>2207</v>
       </c>
       <c r="D1090" s="2"/>
     </row>
@@ -23280,10 +23766,10 @@
         <v>40</v>
       </c>
       <c r="B1091" t="s" s="2">
-        <v>2206</v>
+        <v>2208</v>
       </c>
       <c r="C1091" t="s" s="2">
-        <v>2207</v>
+        <v>2163</v>
       </c>
       <c r="D1091" s="2"/>
     </row>
@@ -23292,10 +23778,10 @@
         <v>40</v>
       </c>
       <c r="B1092" t="s" s="2">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="C1092" t="s" s="2">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="D1092" s="2"/>
     </row>
@@ -23304,10 +23790,10 @@
         <v>40</v>
       </c>
       <c r="B1093" t="s" s="2">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="C1093" t="s" s="2">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="D1093" s="2"/>
     </row>
@@ -23316,10 +23802,10 @@
         <v>40</v>
       </c>
       <c r="B1094" t="s" s="2">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="C1094" t="s" s="2">
-        <v>1033</v>
+        <v>2214</v>
       </c>
       <c r="D1094" s="2"/>
     </row>
@@ -23328,10 +23814,10 @@
         <v>40</v>
       </c>
       <c r="B1095" t="s" s="2">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="C1095" t="s" s="2">
-        <v>2214</v>
+        <v>2216</v>
       </c>
       <c r="D1095" s="2"/>
     </row>
@@ -23340,10 +23826,10 @@
         <v>40</v>
       </c>
       <c r="B1096" t="s" s="2">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="C1096" t="s" s="2">
-        <v>2216</v>
+        <v>2218</v>
       </c>
       <c r="D1096" s="2"/>
     </row>
@@ -23352,10 +23838,10 @@
         <v>40</v>
       </c>
       <c r="B1097" t="s" s="2">
-        <v>2217</v>
+        <v>2219</v>
       </c>
       <c r="C1097" t="s" s="2">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="D1097" s="2"/>
     </row>
@@ -23364,10 +23850,10 @@
         <v>40</v>
       </c>
       <c r="B1098" t="s" s="2">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="C1098" t="s" s="2">
-        <v>2220</v>
+        <v>2222</v>
       </c>
       <c r="D1098" s="2"/>
     </row>
@@ -23376,10 +23862,10 @@
         <v>40</v>
       </c>
       <c r="B1099" t="s" s="2">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="C1099" t="s" s="2">
-        <v>2222</v>
+        <v>2224</v>
       </c>
       <c r="D1099" s="2"/>
     </row>
@@ -23388,10 +23874,10 @@
         <v>40</v>
       </c>
       <c r="B1100" t="s" s="2">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="C1100" t="s" s="2">
-        <v>2224</v>
+        <v>2226</v>
       </c>
       <c r="D1100" s="2"/>
     </row>
@@ -23400,10 +23886,10 @@
         <v>40</v>
       </c>
       <c r="B1101" t="s" s="2">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="C1101" t="s" s="2">
-        <v>2226</v>
+        <v>2228</v>
       </c>
       <c r="D1101" s="2"/>
     </row>
@@ -23412,10 +23898,10 @@
         <v>40</v>
       </c>
       <c r="B1102" t="s" s="2">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="C1102" t="s" s="2">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="D1102" s="2"/>
     </row>
@@ -23424,10 +23910,10 @@
         <v>40</v>
       </c>
       <c r="B1103" t="s" s="2">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="C1103" t="s" s="2">
-        <v>2230</v>
+        <v>2232</v>
       </c>
       <c r="D1103" s="2"/>
     </row>
@@ -23436,10 +23922,10 @@
         <v>40</v>
       </c>
       <c r="B1104" t="s" s="2">
-        <v>2231</v>
+        <v>2233</v>
       </c>
       <c r="C1104" t="s" s="2">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="D1104" s="2"/>
     </row>
@@ -23448,10 +23934,10 @@
         <v>40</v>
       </c>
       <c r="B1105" t="s" s="2">
-        <v>2233</v>
+        <v>2235</v>
       </c>
       <c r="C1105" t="s" s="2">
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="D1105" s="2"/>
     </row>
@@ -23460,10 +23946,10 @@
         <v>40</v>
       </c>
       <c r="B1106" t="s" s="2">
-        <v>2235</v>
+        <v>2237</v>
       </c>
       <c r="C1106" t="s" s="2">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="D1106" s="2"/>
     </row>
@@ -23472,10 +23958,10 @@
         <v>40</v>
       </c>
       <c r="B1107" t="s" s="2">
-        <v>2237</v>
+        <v>2239</v>
       </c>
       <c r="C1107" t="s" s="2">
-        <v>2238</v>
+        <v>2240</v>
       </c>
       <c r="D1107" s="2"/>
     </row>
@@ -23484,10 +23970,10 @@
         <v>40</v>
       </c>
       <c r="B1108" t="s" s="2">
-        <v>2239</v>
+        <v>2241</v>
       </c>
       <c r="C1108" t="s" s="2">
-        <v>2240</v>
+        <v>2242</v>
       </c>
       <c r="D1108" s="2"/>
     </row>
@@ -23496,10 +23982,10 @@
         <v>40</v>
       </c>
       <c r="B1109" t="s" s="2">
-        <v>2241</v>
+        <v>2243</v>
       </c>
       <c r="C1109" t="s" s="2">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="D1109" s="2"/>
     </row>
@@ -23508,10 +23994,10 @@
         <v>40</v>
       </c>
       <c r="B1110" t="s" s="2">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="C1110" t="s" s="2">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="D1110" s="2"/>
     </row>
@@ -23520,10 +24006,10 @@
         <v>40</v>
       </c>
       <c r="B1111" t="s" s="2">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="C1111" t="s" s="2">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="D1111" s="2"/>
     </row>
@@ -23532,10 +24018,10 @@
         <v>40</v>
       </c>
       <c r="B1112" t="s" s="2">
-        <v>2247</v>
+        <v>2249</v>
       </c>
       <c r="C1112" t="s" s="2">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="D1112" s="2"/>
     </row>
@@ -23544,10 +24030,10 @@
         <v>40</v>
       </c>
       <c r="B1113" t="s" s="2">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="C1113" t="s" s="2">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="D1113" s="2"/>
     </row>
@@ -23556,10 +24042,10 @@
         <v>40</v>
       </c>
       <c r="B1114" t="s" s="2">
-        <v>2251</v>
+        <v>2253</v>
       </c>
       <c r="C1114" t="s" s="2">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="D1114" s="2"/>
     </row>
@@ -23568,10 +24054,10 @@
         <v>40</v>
       </c>
       <c r="B1115" t="s" s="2">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="C1115" t="s" s="2">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="D1115" s="2"/>
     </row>
@@ -23580,10 +24066,10 @@
         <v>40</v>
       </c>
       <c r="B1116" t="s" s="2">
-        <v>2255</v>
+        <v>2257</v>
       </c>
       <c r="C1116" t="s" s="2">
-        <v>2256</v>
+        <v>2258</v>
       </c>
       <c r="D1116" s="2"/>
     </row>
@@ -23592,10 +24078,10 @@
         <v>40</v>
       </c>
       <c r="B1117" t="s" s="2">
-        <v>2257</v>
+        <v>2259</v>
       </c>
       <c r="C1117" t="s" s="2">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="D1117" s="2"/>
     </row>
@@ -23604,10 +24090,10 @@
         <v>40</v>
       </c>
       <c r="B1118" t="s" s="2">
-        <v>2259</v>
+        <v>2261</v>
       </c>
       <c r="C1118" t="s" s="2">
-        <v>2260</v>
+        <v>2262</v>
       </c>
       <c r="D1118" s="2"/>
     </row>
@@ -23616,10 +24102,10 @@
         <v>40</v>
       </c>
       <c r="B1119" t="s" s="2">
-        <v>2261</v>
+        <v>2263</v>
       </c>
       <c r="C1119" t="s" s="2">
-        <v>2262</v>
+        <v>2264</v>
       </c>
       <c r="D1119" s="2"/>
     </row>
@@ -23628,10 +24114,10 @@
         <v>40</v>
       </c>
       <c r="B1120" t="s" s="2">
-        <v>2263</v>
+        <v>2265</v>
       </c>
       <c r="C1120" t="s" s="2">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="D1120" s="2"/>
     </row>
@@ -23640,10 +24126,10 @@
         <v>40</v>
       </c>
       <c r="B1121" t="s" s="2">
-        <v>2265</v>
+        <v>2267</v>
       </c>
       <c r="C1121" t="s" s="2">
-        <v>2266</v>
+        <v>2268</v>
       </c>
       <c r="D1121" s="2"/>
     </row>
@@ -23652,10 +24138,10 @@
         <v>40</v>
       </c>
       <c r="B1122" t="s" s="2">
-        <v>2267</v>
+        <v>2269</v>
       </c>
       <c r="C1122" t="s" s="2">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="D1122" s="2"/>
     </row>
@@ -23664,10 +24150,10 @@
         <v>40</v>
       </c>
       <c r="B1123" t="s" s="2">
-        <v>2269</v>
+        <v>2271</v>
       </c>
       <c r="C1123" t="s" s="2">
-        <v>2270</v>
+        <v>2272</v>
       </c>
       <c r="D1123" s="2"/>
     </row>
@@ -23676,10 +24162,10 @@
         <v>40</v>
       </c>
       <c r="B1124" t="s" s="2">
-        <v>2271</v>
+        <v>2273</v>
       </c>
       <c r="C1124" t="s" s="2">
-        <v>2272</v>
+        <v>2274</v>
       </c>
       <c r="D1124" s="2"/>
     </row>
@@ -23688,10 +24174,10 @@
         <v>40</v>
       </c>
       <c r="B1125" t="s" s="2">
-        <v>2273</v>
+        <v>2275</v>
       </c>
       <c r="C1125" t="s" s="2">
-        <v>2274</v>
+        <v>2276</v>
       </c>
       <c r="D1125" s="2"/>
     </row>
@@ -23700,10 +24186,10 @@
         <v>40</v>
       </c>
       <c r="B1126" t="s" s="2">
-        <v>2275</v>
+        <v>2277</v>
       </c>
       <c r="C1126" t="s" s="2">
-        <v>2276</v>
+        <v>2278</v>
       </c>
       <c r="D1126" s="2"/>
     </row>
@@ -23712,10 +24198,10 @@
         <v>40</v>
       </c>
       <c r="B1127" t="s" s="2">
-        <v>2277</v>
+        <v>2279</v>
       </c>
       <c r="C1127" t="s" s="2">
-        <v>2278</v>
+        <v>2280</v>
       </c>
       <c r="D1127" s="2"/>
     </row>
@@ -23724,10 +24210,10 @@
         <v>40</v>
       </c>
       <c r="B1128" t="s" s="2">
-        <v>2279</v>
+        <v>2281</v>
       </c>
       <c r="C1128" t="s" s="2">
-        <v>2280</v>
+        <v>2282</v>
       </c>
       <c r="D1128" s="2"/>
     </row>
@@ -23736,10 +24222,10 @@
         <v>40</v>
       </c>
       <c r="B1129" t="s" s="2">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="C1129" t="s" s="2">
-        <v>2282</v>
+        <v>2284</v>
       </c>
       <c r="D1129" s="2"/>
     </row>
@@ -23748,10 +24234,10 @@
         <v>40</v>
       </c>
       <c r="B1130" t="s" s="2">
-        <v>2283</v>
+        <v>2285</v>
       </c>
       <c r="C1130" t="s" s="2">
-        <v>2284</v>
+        <v>2286</v>
       </c>
       <c r="D1130" s="2"/>
     </row>
@@ -23760,10 +24246,10 @@
         <v>40</v>
       </c>
       <c r="B1131" t="s" s="2">
-        <v>2285</v>
+        <v>2287</v>
       </c>
       <c r="C1131" t="s" s="2">
-        <v>2286</v>
+        <v>2288</v>
       </c>
       <c r="D1131" s="2"/>
     </row>
@@ -23772,10 +24258,10 @@
         <v>40</v>
       </c>
       <c r="B1132" t="s" s="2">
-        <v>2287</v>
+        <v>2289</v>
       </c>
       <c r="C1132" t="s" s="2">
-        <v>2288</v>
+        <v>2290</v>
       </c>
       <c r="D1132" s="2"/>
     </row>
@@ -23784,10 +24270,10 @@
         <v>40</v>
       </c>
       <c r="B1133" t="s" s="2">
-        <v>2289</v>
+        <v>2291</v>
       </c>
       <c r="C1133" t="s" s="2">
-        <v>2290</v>
+        <v>2141</v>
       </c>
       <c r="D1133" s="2"/>
     </row>
@@ -23796,10 +24282,10 @@
         <v>40</v>
       </c>
       <c r="B1134" t="s" s="2">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="C1134" t="s" s="2">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="D1134" s="2"/>
     </row>
@@ -23808,10 +24294,10 @@
         <v>40</v>
       </c>
       <c r="B1135" t="s" s="2">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="C1135" t="s" s="2">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="D1135" s="2"/>
     </row>
@@ -23820,10 +24306,10 @@
         <v>40</v>
       </c>
       <c r="B1136" t="s" s="2">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="C1136" t="s" s="2">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="D1136" s="2"/>
     </row>
@@ -23832,10 +24318,10 @@
         <v>40</v>
       </c>
       <c r="B1137" t="s" s="2">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="C1137" t="s" s="2">
-        <v>2298</v>
+        <v>1119</v>
       </c>
       <c r="D1137" s="2"/>
     </row>
@@ -24771,7 +25257,7 @@
         <v>2453</v>
       </c>
       <c r="C1215" t="s" s="2">
-        <v>2402</v>
+        <v>2454</v>
       </c>
       <c r="D1215" s="2"/>
     </row>
@@ -24780,10 +25266,10 @@
         <v>40</v>
       </c>
       <c r="B1216" t="s" s="2">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="C1216" t="s" s="2">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="D1216" s="2"/>
     </row>
@@ -24792,10 +25278,10 @@
         <v>40</v>
       </c>
       <c r="B1217" t="s" s="2">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="C1217" t="s" s="2">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="D1217" s="2"/>
     </row>
@@ -24804,10 +25290,10 @@
         <v>40</v>
       </c>
       <c r="B1218" t="s" s="2">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="C1218" t="s" s="2">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="D1218" s="2"/>
     </row>
@@ -24816,10 +25302,10 @@
         <v>40</v>
       </c>
       <c r="B1219" t="s" s="2">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="C1219" t="s" s="2">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="D1219" s="2"/>
     </row>
@@ -24828,10 +25314,10 @@
         <v>40</v>
       </c>
       <c r="B1220" t="s" s="2">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="C1220" t="s" s="2">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="D1220" s="2"/>
     </row>
@@ -24840,10 +25326,10 @@
         <v>40</v>
       </c>
       <c r="B1221" t="s" s="2">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="C1221" t="s" s="2">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="D1221" s="2"/>
     </row>
@@ -24852,10 +25338,10 @@
         <v>40</v>
       </c>
       <c r="B1222" t="s" s="2">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="C1222" t="s" s="2">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="D1222" s="2"/>
     </row>
@@ -24864,10 +25350,10 @@
         <v>40</v>
       </c>
       <c r="B1223" t="s" s="2">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="C1223" t="s" s="2">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="D1223" s="2"/>
     </row>
@@ -24876,10 +25362,10 @@
         <v>40</v>
       </c>
       <c r="B1224" t="s" s="2">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="C1224" t="s" s="2">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="D1224" s="2"/>
     </row>
@@ -24888,10 +25374,10 @@
         <v>40</v>
       </c>
       <c r="B1225" t="s" s="2">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="C1225" t="s" s="2">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="D1225" s="2"/>
     </row>
@@ -24900,10 +25386,10 @@
         <v>40</v>
       </c>
       <c r="B1226" t="s" s="2">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="C1226" t="s" s="2">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="D1226" s="2"/>
     </row>
@@ -24912,10 +25398,10 @@
         <v>40</v>
       </c>
       <c r="B1227" t="s" s="2">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="C1227" t="s" s="2">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="D1227" s="2"/>
     </row>
@@ -24924,10 +25410,10 @@
         <v>40</v>
       </c>
       <c r="B1228" t="s" s="2">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="C1228" t="s" s="2">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="D1228" s="2"/>
     </row>
@@ -24936,10 +25422,10 @@
         <v>40</v>
       </c>
       <c r="B1229" t="s" s="2">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="C1229" t="s" s="2">
-        <v>2481</v>
+        <v>2482</v>
       </c>
       <c r="D1229" s="2"/>
     </row>
@@ -24948,10 +25434,10 @@
         <v>40</v>
       </c>
       <c r="B1230" t="s" s="2">
-        <v>2482</v>
+        <v>2483</v>
       </c>
       <c r="C1230" t="s" s="2">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="D1230" s="2"/>
     </row>
@@ -24960,10 +25446,10 @@
         <v>40</v>
       </c>
       <c r="B1231" t="s" s="2">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="C1231" t="s" s="2">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="D1231" s="2"/>
     </row>
@@ -24972,10 +25458,10 @@
         <v>40</v>
       </c>
       <c r="B1232" t="s" s="2">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="C1232" t="s" s="2">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="D1232" s="2"/>
     </row>
@@ -24984,10 +25470,10 @@
         <v>40</v>
       </c>
       <c r="B1233" t="s" s="2">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="C1233" t="s" s="2">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="D1233" s="2"/>
     </row>
@@ -24996,10 +25482,10 @@
         <v>40</v>
       </c>
       <c r="B1234" t="s" s="2">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="C1234" t="s" s="2">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="D1234" s="2"/>
     </row>
@@ -25008,10 +25494,10 @@
         <v>40</v>
       </c>
       <c r="B1235" t="s" s="2">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="C1235" t="s" s="2">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="D1235" s="2"/>
     </row>
@@ -25020,10 +25506,10 @@
         <v>40</v>
       </c>
       <c r="B1236" t="s" s="2">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="C1236" t="s" s="2">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="D1236" s="2"/>
     </row>
@@ -25032,10 +25518,10 @@
         <v>40</v>
       </c>
       <c r="B1237" t="s" s="2">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="C1237" t="s" s="2">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="D1237" s="2"/>
     </row>
@@ -25044,10 +25530,10 @@
         <v>40</v>
       </c>
       <c r="B1238" t="s" s="2">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="C1238" t="s" s="2">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D1238" s="2"/>
     </row>
@@ -25056,10 +25542,10 @@
         <v>40</v>
       </c>
       <c r="B1239" t="s" s="2">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="C1239" t="s" s="2">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="D1239" s="2"/>
     </row>
@@ -25068,10 +25554,10 @@
         <v>40</v>
       </c>
       <c r="B1240" t="s" s="2">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="C1240" t="s" s="2">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="D1240" s="2"/>
     </row>
@@ -25080,10 +25566,10 @@
         <v>40</v>
       </c>
       <c r="B1241" t="s" s="2">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="C1241" t="s" s="2">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="D1241" s="2"/>
     </row>
@@ -25092,10 +25578,10 @@
         <v>40</v>
       </c>
       <c r="B1242" t="s" s="2">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="C1242" t="s" s="2">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="D1242" s="2"/>
     </row>
@@ -25104,10 +25590,10 @@
         <v>40</v>
       </c>
       <c r="B1243" t="s" s="2">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="C1243" t="s" s="2">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="D1243" s="2"/>
     </row>
@@ -25116,10 +25602,10 @@
         <v>40</v>
       </c>
       <c r="B1244" t="s" s="2">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="C1244" t="s" s="2">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="D1244" s="2"/>
     </row>
@@ -25128,10 +25614,10 @@
         <v>40</v>
       </c>
       <c r="B1245" t="s" s="2">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="C1245" t="s" s="2">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="D1245" s="2"/>
     </row>
@@ -25140,10 +25626,10 @@
         <v>40</v>
       </c>
       <c r="B1246" t="s" s="2">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="C1246" t="s" s="2">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="D1246" s="2"/>
     </row>
@@ -25152,10 +25638,10 @@
         <v>40</v>
       </c>
       <c r="B1247" t="s" s="2">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="C1247" t="s" s="2">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="D1247" s="2"/>
     </row>
@@ -25164,10 +25650,10 @@
         <v>40</v>
       </c>
       <c r="B1248" t="s" s="2">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="C1248" t="s" s="2">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="D1248" s="2"/>
     </row>
@@ -25176,10 +25662,10 @@
         <v>40</v>
       </c>
       <c r="B1249" t="s" s="2">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="C1249" t="s" s="2">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="D1249" s="2"/>
     </row>
@@ -25188,10 +25674,10 @@
         <v>40</v>
       </c>
       <c r="B1250" t="s" s="2">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="C1250" t="s" s="2">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="D1250" s="2"/>
     </row>
@@ -25200,10 +25686,10 @@
         <v>40</v>
       </c>
       <c r="B1251" t="s" s="2">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="C1251" t="s" s="2">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="D1251" s="2"/>
     </row>
@@ -25212,10 +25698,10 @@
         <v>40</v>
       </c>
       <c r="B1252" t="s" s="2">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="C1252" t="s" s="2">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="D1252" s="2"/>
     </row>
@@ -25224,10 +25710,10 @@
         <v>40</v>
       </c>
       <c r="B1253" t="s" s="2">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="C1253" t="s" s="2">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="D1253" s="2"/>
     </row>
@@ -25236,10 +25722,10 @@
         <v>40</v>
       </c>
       <c r="B1254" t="s" s="2">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="C1254" t="s" s="2">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="D1254" s="2"/>
     </row>
@@ -25248,10 +25734,10 @@
         <v>40</v>
       </c>
       <c r="B1255" t="s" s="2">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="C1255" t="s" s="2">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="D1255" s="2"/>
     </row>
@@ -25260,10 +25746,10 @@
         <v>40</v>
       </c>
       <c r="B1256" t="s" s="2">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="C1256" t="s" s="2">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="D1256" s="2"/>
     </row>
@@ -25272,10 +25758,10 @@
         <v>40</v>
       </c>
       <c r="B1257" t="s" s="2">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="C1257" t="s" s="2">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="D1257" s="2"/>
     </row>
@@ -25284,10 +25770,10 @@
         <v>40</v>
       </c>
       <c r="B1258" t="s" s="2">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="C1258" t="s" s="2">
-        <v>2539</v>
+        <v>2540</v>
       </c>
       <c r="D1258" s="2"/>
     </row>
@@ -25296,10 +25782,10 @@
         <v>40</v>
       </c>
       <c r="B1259" t="s" s="2">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="C1259" t="s" s="2">
-        <v>2541</v>
+        <v>2542</v>
       </c>
       <c r="D1259" s="2"/>
     </row>
@@ -25308,10 +25794,10 @@
         <v>40</v>
       </c>
       <c r="B1260" t="s" s="2">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="C1260" t="s" s="2">
-        <v>2543</v>
+        <v>2492</v>
       </c>
       <c r="D1260" s="2"/>
     </row>
@@ -26739,7 +27225,7 @@
         <v>2780</v>
       </c>
       <c r="C1379" t="s" s="2">
-        <v>559</v>
+        <v>2781</v>
       </c>
       <c r="D1379" s="2"/>
     </row>
@@ -26748,10 +27234,10 @@
         <v>40</v>
       </c>
       <c r="B1380" t="s" s="2">
-        <v>2781</v>
+        <v>2782</v>
       </c>
       <c r="C1380" t="s" s="2">
-        <v>559</v>
+        <v>2783</v>
       </c>
       <c r="D1380" s="2"/>
     </row>
@@ -26760,10 +27246,10 @@
         <v>40</v>
       </c>
       <c r="B1381" t="s" s="2">
-        <v>2782</v>
+        <v>2784</v>
       </c>
       <c r="C1381" t="s" s="2">
-        <v>559</v>
+        <v>2785</v>
       </c>
       <c r="D1381" s="2"/>
     </row>
@@ -26772,10 +27258,10 @@
         <v>40</v>
       </c>
       <c r="B1382" t="s" s="2">
-        <v>2783</v>
+        <v>2786</v>
       </c>
       <c r="C1382" t="s" s="2">
-        <v>559</v>
+        <v>2787</v>
       </c>
       <c r="D1382" s="2"/>
     </row>
@@ -26784,10 +27270,10 @@
         <v>40</v>
       </c>
       <c r="B1383" t="s" s="2">
-        <v>2784</v>
+        <v>2788</v>
       </c>
       <c r="C1383" t="s" s="2">
-        <v>559</v>
+        <v>2789</v>
       </c>
       <c r="D1383" s="2"/>
     </row>
@@ -26796,10 +27282,10 @@
         <v>40</v>
       </c>
       <c r="B1384" t="s" s="2">
-        <v>2785</v>
+        <v>2790</v>
       </c>
       <c r="C1384" t="s" s="2">
-        <v>559</v>
+        <v>2791</v>
       </c>
       <c r="D1384" s="2"/>
     </row>
@@ -26808,10 +27294,10 @@
         <v>40</v>
       </c>
       <c r="B1385" t="s" s="2">
-        <v>2786</v>
+        <v>2792</v>
       </c>
       <c r="C1385" t="s" s="2">
-        <v>559</v>
+        <v>2793</v>
       </c>
       <c r="D1385" s="2"/>
     </row>
@@ -26820,10 +27306,10 @@
         <v>40</v>
       </c>
       <c r="B1386" t="s" s="2">
-        <v>2787</v>
+        <v>2794</v>
       </c>
       <c r="C1386" t="s" s="2">
-        <v>2788</v>
+        <v>2795</v>
       </c>
       <c r="D1386" s="2"/>
     </row>
@@ -26832,10 +27318,10 @@
         <v>40</v>
       </c>
       <c r="B1387" t="s" s="2">
-        <v>2789</v>
+        <v>2796</v>
       </c>
       <c r="C1387" t="s" s="2">
-        <v>2790</v>
+        <v>2797</v>
       </c>
       <c r="D1387" s="2"/>
     </row>
@@ -26844,10 +27330,10 @@
         <v>40</v>
       </c>
       <c r="B1388" t="s" s="2">
-        <v>2791</v>
+        <v>2798</v>
       </c>
       <c r="C1388" t="s" s="2">
-        <v>2792</v>
+        <v>2799</v>
       </c>
       <c r="D1388" s="2"/>
     </row>
@@ -26856,10 +27342,10 @@
         <v>40</v>
       </c>
       <c r="B1389" t="s" s="2">
-        <v>2793</v>
+        <v>2800</v>
       </c>
       <c r="C1389" t="s" s="2">
-        <v>2794</v>
+        <v>2801</v>
       </c>
       <c r="D1389" s="2"/>
     </row>
@@ -26868,10 +27354,10 @@
         <v>40</v>
       </c>
       <c r="B1390" t="s" s="2">
-        <v>2795</v>
+        <v>2802</v>
       </c>
       <c r="C1390" t="s" s="2">
-        <v>2796</v>
+        <v>2803</v>
       </c>
       <c r="D1390" s="2"/>
     </row>
@@ -26880,10 +27366,10 @@
         <v>40</v>
       </c>
       <c r="B1391" t="s" s="2">
-        <v>2797</v>
+        <v>2804</v>
       </c>
       <c r="C1391" t="s" s="2">
-        <v>2798</v>
+        <v>2805</v>
       </c>
       <c r="D1391" s="2"/>
     </row>
@@ -26892,10 +27378,10 @@
         <v>40</v>
       </c>
       <c r="B1392" t="s" s="2">
-        <v>2799</v>
+        <v>2806</v>
       </c>
       <c r="C1392" t="s" s="2">
-        <v>2800</v>
+        <v>2807</v>
       </c>
       <c r="D1392" s="2"/>
     </row>
@@ -26904,10 +27390,10 @@
         <v>40</v>
       </c>
       <c r="B1393" t="s" s="2">
-        <v>2801</v>
+        <v>2808</v>
       </c>
       <c r="C1393" t="s" s="2">
-        <v>2802</v>
+        <v>2809</v>
       </c>
       <c r="D1393" s="2"/>
     </row>
@@ -26916,10 +27402,10 @@
         <v>40</v>
       </c>
       <c r="B1394" t="s" s="2">
-        <v>2803</v>
+        <v>2810</v>
       </c>
       <c r="C1394" t="s" s="2">
-        <v>2804</v>
+        <v>2811</v>
       </c>
       <c r="D1394" s="2"/>
     </row>
@@ -26928,10 +27414,10 @@
         <v>40</v>
       </c>
       <c r="B1395" t="s" s="2">
-        <v>2805</v>
+        <v>2812</v>
       </c>
       <c r="C1395" t="s" s="2">
-        <v>2806</v>
+        <v>2813</v>
       </c>
       <c r="D1395" s="2"/>
     </row>
@@ -26940,10 +27426,10 @@
         <v>40</v>
       </c>
       <c r="B1396" t="s" s="2">
-        <v>2807</v>
+        <v>2814</v>
       </c>
       <c r="C1396" t="s" s="2">
-        <v>2808</v>
+        <v>2815</v>
       </c>
       <c r="D1396" s="2"/>
     </row>
@@ -26952,10 +27438,10 @@
         <v>40</v>
       </c>
       <c r="B1397" t="s" s="2">
-        <v>2809</v>
+        <v>2816</v>
       </c>
       <c r="C1397" t="s" s="2">
-        <v>2810</v>
+        <v>2817</v>
       </c>
       <c r="D1397" s="2"/>
     </row>
@@ -26964,10 +27450,10 @@
         <v>40</v>
       </c>
       <c r="B1398" t="s" s="2">
-        <v>2811</v>
+        <v>2818</v>
       </c>
       <c r="C1398" t="s" s="2">
-        <v>2812</v>
+        <v>2819</v>
       </c>
       <c r="D1398" s="2"/>
     </row>
@@ -26976,10 +27462,10 @@
         <v>40</v>
       </c>
       <c r="B1399" t="s" s="2">
-        <v>2813</v>
+        <v>2820</v>
       </c>
       <c r="C1399" t="s" s="2">
-        <v>2814</v>
+        <v>2821</v>
       </c>
       <c r="D1399" s="2"/>
     </row>
@@ -26988,10 +27474,10 @@
         <v>40</v>
       </c>
       <c r="B1400" t="s" s="2">
-        <v>2815</v>
+        <v>2822</v>
       </c>
       <c r="C1400" t="s" s="2">
-        <v>2816</v>
+        <v>2823</v>
       </c>
       <c r="D1400" s="2"/>
     </row>
@@ -27000,10 +27486,10 @@
         <v>40</v>
       </c>
       <c r="B1401" t="s" s="2">
-        <v>2817</v>
+        <v>2824</v>
       </c>
       <c r="C1401" t="s" s="2">
-        <v>2818</v>
+        <v>2825</v>
       </c>
       <c r="D1401" s="2"/>
     </row>
@@ -27012,10 +27498,10 @@
         <v>40</v>
       </c>
       <c r="B1402" t="s" s="2">
-        <v>2819</v>
+        <v>2826</v>
       </c>
       <c r="C1402" t="s" s="2">
-        <v>2820</v>
+        <v>2827</v>
       </c>
       <c r="D1402" s="2"/>
     </row>
@@ -27024,10 +27510,10 @@
         <v>40</v>
       </c>
       <c r="B1403" t="s" s="2">
-        <v>2821</v>
+        <v>2828</v>
       </c>
       <c r="C1403" t="s" s="2">
-        <v>2822</v>
+        <v>2829</v>
       </c>
       <c r="D1403" s="2"/>
     </row>
@@ -27036,10 +27522,10 @@
         <v>40</v>
       </c>
       <c r="B1404" t="s" s="2">
-        <v>2823</v>
+        <v>2830</v>
       </c>
       <c r="C1404" t="s" s="2">
-        <v>2824</v>
+        <v>2831</v>
       </c>
       <c r="D1404" s="2"/>
     </row>
@@ -27048,10 +27534,10 @@
         <v>40</v>
       </c>
       <c r="B1405" t="s" s="2">
-        <v>2825</v>
+        <v>2832</v>
       </c>
       <c r="C1405" t="s" s="2">
-        <v>2826</v>
+        <v>2833</v>
       </c>
       <c r="D1405" s="2"/>
     </row>
@@ -27060,10 +27546,10 @@
         <v>40</v>
       </c>
       <c r="B1406" t="s" s="2">
-        <v>2827</v>
+        <v>2834</v>
       </c>
       <c r="C1406" t="s" s="2">
-        <v>2828</v>
+        <v>2835</v>
       </c>
       <c r="D1406" s="2"/>
     </row>
@@ -27072,10 +27558,10 @@
         <v>40</v>
       </c>
       <c r="B1407" t="s" s="2">
-        <v>2829</v>
+        <v>2836</v>
       </c>
       <c r="C1407" t="s" s="2">
-        <v>2830</v>
+        <v>2837</v>
       </c>
       <c r="D1407" s="2"/>
     </row>
@@ -27084,10 +27570,10 @@
         <v>40</v>
       </c>
       <c r="B1408" t="s" s="2">
-        <v>2831</v>
+        <v>2838</v>
       </c>
       <c r="C1408" t="s" s="2">
-        <v>2832</v>
+        <v>2839</v>
       </c>
       <c r="D1408" s="2"/>
     </row>
@@ -27096,10 +27582,10 @@
         <v>40</v>
       </c>
       <c r="B1409" t="s" s="2">
-        <v>2833</v>
+        <v>2840</v>
       </c>
       <c r="C1409" t="s" s="2">
-        <v>2834</v>
+        <v>2841</v>
       </c>
       <c r="D1409" s="2"/>
     </row>
@@ -27108,10 +27594,10 @@
         <v>40</v>
       </c>
       <c r="B1410" t="s" s="2">
-        <v>2835</v>
+        <v>2842</v>
       </c>
       <c r="C1410" t="s" s="2">
-        <v>2788</v>
+        <v>2843</v>
       </c>
       <c r="D1410" s="2"/>
     </row>
@@ -27120,10 +27606,10 @@
         <v>40</v>
       </c>
       <c r="B1411" t="s" s="2">
-        <v>2836</v>
+        <v>2844</v>
       </c>
       <c r="C1411" t="s" s="2">
-        <v>2837</v>
+        <v>2845</v>
       </c>
       <c r="D1411" s="2"/>
     </row>
@@ -27132,10 +27618,10 @@
         <v>40</v>
       </c>
       <c r="B1412" t="s" s="2">
-        <v>2838</v>
+        <v>2846</v>
       </c>
       <c r="C1412" t="s" s="2">
-        <v>2839</v>
+        <v>2847</v>
       </c>
       <c r="D1412" s="2"/>
     </row>
@@ -27144,10 +27630,10 @@
         <v>40</v>
       </c>
       <c r="B1413" t="s" s="2">
-        <v>2840</v>
+        <v>2848</v>
       </c>
       <c r="C1413" t="s" s="2">
-        <v>2841</v>
+        <v>2849</v>
       </c>
       <c r="D1413" s="2"/>
     </row>
@@ -27156,10 +27642,10 @@
         <v>40</v>
       </c>
       <c r="B1414" t="s" s="2">
-        <v>2842</v>
+        <v>2850</v>
       </c>
       <c r="C1414" t="s" s="2">
-        <v>2843</v>
+        <v>2851</v>
       </c>
       <c r="D1414" s="2"/>
     </row>
@@ -27168,10 +27654,10 @@
         <v>40</v>
       </c>
       <c r="B1415" t="s" s="2">
-        <v>2844</v>
+        <v>2852</v>
       </c>
       <c r="C1415" t="s" s="2">
-        <v>2845</v>
+        <v>2853</v>
       </c>
       <c r="D1415" s="2"/>
     </row>
@@ -27180,10 +27666,10 @@
         <v>40</v>
       </c>
       <c r="B1416" t="s" s="2">
-        <v>2846</v>
+        <v>2854</v>
       </c>
       <c r="C1416" t="s" s="2">
-        <v>2847</v>
+        <v>2855</v>
       </c>
       <c r="D1416" s="2"/>
     </row>
@@ -27192,10 +27678,10 @@
         <v>40</v>
       </c>
       <c r="B1417" t="s" s="2">
-        <v>2848</v>
+        <v>2856</v>
       </c>
       <c r="C1417" t="s" s="2">
-        <v>2849</v>
+        <v>2857</v>
       </c>
       <c r="D1417" s="2"/>
     </row>
@@ -27204,10 +27690,10 @@
         <v>40</v>
       </c>
       <c r="B1418" t="s" s="2">
-        <v>2850</v>
+        <v>2858</v>
       </c>
       <c r="C1418" t="s" s="2">
-        <v>2851</v>
+        <v>2859</v>
       </c>
       <c r="D1418" s="2"/>
     </row>
@@ -27216,10 +27702,10 @@
         <v>40</v>
       </c>
       <c r="B1419" t="s" s="2">
-        <v>2852</v>
+        <v>2860</v>
       </c>
       <c r="C1419" t="s" s="2">
-        <v>2853</v>
+        <v>2861</v>
       </c>
       <c r="D1419" s="2"/>
     </row>
@@ -27228,10 +27714,10 @@
         <v>40</v>
       </c>
       <c r="B1420" t="s" s="2">
-        <v>2854</v>
+        <v>2862</v>
       </c>
       <c r="C1420" t="s" s="2">
-        <v>2855</v>
+        <v>2863</v>
       </c>
       <c r="D1420" s="2"/>
     </row>
@@ -27240,10 +27726,10 @@
         <v>40</v>
       </c>
       <c r="B1421" t="s" s="2">
-        <v>2856</v>
+        <v>2864</v>
       </c>
       <c r="C1421" t="s" s="2">
-        <v>2857</v>
+        <v>2865</v>
       </c>
       <c r="D1421" s="2"/>
     </row>
@@ -27252,10 +27738,10 @@
         <v>40</v>
       </c>
       <c r="B1422" t="s" s="2">
-        <v>2858</v>
+        <v>2866</v>
       </c>
       <c r="C1422" t="s" s="2">
-        <v>2859</v>
+        <v>2867</v>
       </c>
       <c r="D1422" s="2"/>
     </row>
@@ -27264,10 +27750,10 @@
         <v>40</v>
       </c>
       <c r="B1423" t="s" s="2">
-        <v>2860</v>
+        <v>2868</v>
       </c>
       <c r="C1423" t="s" s="2">
-        <v>2861</v>
+        <v>2869</v>
       </c>
       <c r="D1423" s="2"/>
     </row>
@@ -27276,10 +27762,10 @@
         <v>40</v>
       </c>
       <c r="B1424" t="s" s="2">
-        <v>2862</v>
+        <v>2870</v>
       </c>
       <c r="C1424" t="s" s="2">
-        <v>2863</v>
+        <v>2871</v>
       </c>
       <c r="D1424" s="2"/>
     </row>
@@ -27288,10 +27774,10 @@
         <v>40</v>
       </c>
       <c r="B1425" t="s" s="2">
-        <v>2864</v>
+        <v>2872</v>
       </c>
       <c r="C1425" t="s" s="2">
-        <v>2865</v>
+        <v>2873</v>
       </c>
       <c r="D1425" s="2"/>
     </row>
@@ -27300,10 +27786,10 @@
         <v>40</v>
       </c>
       <c r="B1426" t="s" s="2">
-        <v>2866</v>
+        <v>2874</v>
       </c>
       <c r="C1426" t="s" s="2">
-        <v>2867</v>
+        <v>2875</v>
       </c>
       <c r="D1426" s="2"/>
     </row>
@@ -27312,10 +27798,10 @@
         <v>40</v>
       </c>
       <c r="B1427" t="s" s="2">
-        <v>2868</v>
+        <v>2876</v>
       </c>
       <c r="C1427" t="s" s="2">
-        <v>2869</v>
+        <v>2877</v>
       </c>
       <c r="D1427" s="2"/>
     </row>
@@ -27324,10 +27810,10 @@
         <v>40</v>
       </c>
       <c r="B1428" t="s" s="2">
-        <v>2870</v>
+        <v>2878</v>
       </c>
       <c r="C1428" t="s" s="2">
-        <v>2871</v>
+        <v>2879</v>
       </c>
       <c r="D1428" s="2"/>
     </row>
@@ -27336,10 +27822,10 @@
         <v>40</v>
       </c>
       <c r="B1429" t="s" s="2">
-        <v>2872</v>
+        <v>2880</v>
       </c>
       <c r="C1429" t="s" s="2">
-        <v>2873</v>
+        <v>561</v>
       </c>
       <c r="D1429" s="2"/>
     </row>
@@ -27348,10 +27834,10 @@
         <v>40</v>
       </c>
       <c r="B1430" t="s" s="2">
-        <v>2874</v>
+        <v>2881</v>
       </c>
       <c r="C1430" t="s" s="2">
-        <v>2875</v>
+        <v>561</v>
       </c>
       <c r="D1430" s="2"/>
     </row>
@@ -27360,10 +27846,10 @@
         <v>40</v>
       </c>
       <c r="B1431" t="s" s="2">
-        <v>2876</v>
+        <v>2882</v>
       </c>
       <c r="C1431" t="s" s="2">
-        <v>2877</v>
+        <v>2883</v>
       </c>
       <c r="D1431" s="2"/>
     </row>
@@ -27372,10 +27858,10 @@
         <v>40</v>
       </c>
       <c r="B1432" t="s" s="2">
-        <v>2878</v>
+        <v>2884</v>
       </c>
       <c r="C1432" t="s" s="2">
-        <v>2879</v>
+        <v>2885</v>
       </c>
       <c r="D1432" s="2"/>
     </row>
@@ -27384,10 +27870,10 @@
         <v>40</v>
       </c>
       <c r="B1433" t="s" s="2">
-        <v>2880</v>
+        <v>2886</v>
       </c>
       <c r="C1433" t="s" s="2">
-        <v>2881</v>
+        <v>2887</v>
       </c>
       <c r="D1433" s="2"/>
     </row>
@@ -27396,10 +27882,10 @@
         <v>40</v>
       </c>
       <c r="B1434" t="s" s="2">
-        <v>2882</v>
+        <v>2888</v>
       </c>
       <c r="C1434" t="s" s="2">
-        <v>2883</v>
+        <v>2889</v>
       </c>
       <c r="D1434" s="2"/>
     </row>
@@ -27408,10 +27894,10 @@
         <v>40</v>
       </c>
       <c r="B1435" t="s" s="2">
-        <v>2884</v>
+        <v>2890</v>
       </c>
       <c r="C1435" t="s" s="2">
-        <v>2885</v>
+        <v>2891</v>
       </c>
       <c r="D1435" s="2"/>
     </row>
@@ -27420,10 +27906,10 @@
         <v>40</v>
       </c>
       <c r="B1436" t="s" s="2">
-        <v>2886</v>
+        <v>2892</v>
       </c>
       <c r="C1436" t="s" s="2">
-        <v>2887</v>
+        <v>2893</v>
       </c>
       <c r="D1436" s="2"/>
     </row>
@@ -27432,10 +27918,10 @@
         <v>40</v>
       </c>
       <c r="B1437" t="s" s="2">
-        <v>2888</v>
+        <v>2894</v>
       </c>
       <c r="C1437" t="s" s="2">
-        <v>2889</v>
+        <v>2895</v>
       </c>
       <c r="D1437" s="2"/>
     </row>
@@ -27444,10 +27930,10 @@
         <v>40</v>
       </c>
       <c r="B1438" t="s" s="2">
-        <v>2890</v>
+        <v>2896</v>
       </c>
       <c r="C1438" t="s" s="2">
-        <v>2891</v>
+        <v>2897</v>
       </c>
       <c r="D1438" s="2"/>
     </row>
@@ -27456,10 +27942,10 @@
         <v>40</v>
       </c>
       <c r="B1439" t="s" s="2">
-        <v>2892</v>
+        <v>2898</v>
       </c>
       <c r="C1439" t="s" s="2">
-        <v>2893</v>
+        <v>2899</v>
       </c>
       <c r="D1439" s="2"/>
     </row>
@@ -27468,10 +27954,10 @@
         <v>40</v>
       </c>
       <c r="B1440" t="s" s="2">
-        <v>2894</v>
+        <v>2900</v>
       </c>
       <c r="C1440" t="s" s="2">
-        <v>2895</v>
+        <v>2901</v>
       </c>
       <c r="D1440" s="2"/>
     </row>
@@ -27480,10 +27966,10 @@
         <v>40</v>
       </c>
       <c r="B1441" t="s" s="2">
-        <v>2896</v>
+        <v>2902</v>
       </c>
       <c r="C1441" t="s" s="2">
-        <v>2897</v>
+        <v>2903</v>
       </c>
       <c r="D1441" s="2"/>
     </row>
@@ -27492,10 +27978,10 @@
         <v>40</v>
       </c>
       <c r="B1442" t="s" s="2">
-        <v>2898</v>
+        <v>2904</v>
       </c>
       <c r="C1442" t="s" s="2">
-        <v>2899</v>
+        <v>2905</v>
       </c>
       <c r="D1442" s="2"/>
     </row>
@@ -27504,10 +27990,10 @@
         <v>40</v>
       </c>
       <c r="B1443" t="s" s="2">
-        <v>2900</v>
+        <v>2906</v>
       </c>
       <c r="C1443" t="s" s="2">
-        <v>2901</v>
+        <v>2907</v>
       </c>
       <c r="D1443" s="2"/>
     </row>
@@ -27516,10 +28002,10 @@
         <v>40</v>
       </c>
       <c r="B1444" t="s" s="2">
-        <v>2902</v>
+        <v>2908</v>
       </c>
       <c r="C1444" t="s" s="2">
-        <v>2903</v>
+        <v>2909</v>
       </c>
       <c r="D1444" s="2"/>
     </row>
@@ -27528,10 +28014,10 @@
         <v>40</v>
       </c>
       <c r="B1445" t="s" s="2">
-        <v>2904</v>
+        <v>2910</v>
       </c>
       <c r="C1445" t="s" s="2">
-        <v>2905</v>
+        <v>2911</v>
       </c>
       <c r="D1445" s="2"/>
     </row>
@@ -27540,10 +28026,10 @@
         <v>40</v>
       </c>
       <c r="B1446" t="s" s="2">
-        <v>2906</v>
+        <v>2912</v>
       </c>
       <c r="C1446" t="s" s="2">
-        <v>2907</v>
+        <v>2913</v>
       </c>
       <c r="D1446" s="2"/>
     </row>
@@ -27552,10 +28038,10 @@
         <v>40</v>
       </c>
       <c r="B1447" t="s" s="2">
-        <v>2908</v>
+        <v>2914</v>
       </c>
       <c r="C1447" t="s" s="2">
-        <v>2909</v>
+        <v>2915</v>
       </c>
       <c r="D1447" s="2"/>
     </row>
@@ -27564,10 +28050,10 @@
         <v>40</v>
       </c>
       <c r="B1448" t="s" s="2">
-        <v>2910</v>
+        <v>2916</v>
       </c>
       <c r="C1448" t="s" s="2">
-        <v>2911</v>
+        <v>2917</v>
       </c>
       <c r="D1448" s="2"/>
     </row>
@@ -27576,10 +28062,10 @@
         <v>40</v>
       </c>
       <c r="B1449" t="s" s="2">
-        <v>2912</v>
+        <v>2918</v>
       </c>
       <c r="C1449" t="s" s="2">
-        <v>2913</v>
+        <v>2919</v>
       </c>
       <c r="D1449" s="2"/>
     </row>
@@ -27588,10 +28074,10 @@
         <v>40</v>
       </c>
       <c r="B1450" t="s" s="2">
-        <v>2914</v>
+        <v>2920</v>
       </c>
       <c r="C1450" t="s" s="2">
-        <v>2915</v>
+        <v>2921</v>
       </c>
       <c r="D1450" s="2"/>
     </row>
@@ -27600,10 +28086,10 @@
         <v>40</v>
       </c>
       <c r="B1451" t="s" s="2">
-        <v>2916</v>
+        <v>2922</v>
       </c>
       <c r="C1451" t="s" s="2">
-        <v>2917</v>
+        <v>2923</v>
       </c>
       <c r="D1451" s="2"/>
     </row>
@@ -27612,10 +28098,10 @@
         <v>40</v>
       </c>
       <c r="B1452" t="s" s="2">
-        <v>2918</v>
+        <v>2924</v>
       </c>
       <c r="C1452" t="s" s="2">
-        <v>2919</v>
+        <v>2925</v>
       </c>
       <c r="D1452" s="2"/>
     </row>
@@ -27624,10 +28110,10 @@
         <v>40</v>
       </c>
       <c r="B1453" t="s" s="2">
-        <v>2920</v>
+        <v>2926</v>
       </c>
       <c r="C1453" t="s" s="2">
-        <v>2921</v>
+        <v>2927</v>
       </c>
       <c r="D1453" s="2"/>
     </row>
@@ -27636,10 +28122,10 @@
         <v>40</v>
       </c>
       <c r="B1454" t="s" s="2">
-        <v>2922</v>
+        <v>2928</v>
       </c>
       <c r="C1454" t="s" s="2">
-        <v>2923</v>
+        <v>2929</v>
       </c>
       <c r="D1454" s="2"/>
     </row>
@@ -27648,10 +28134,10 @@
         <v>40</v>
       </c>
       <c r="B1455" t="s" s="2">
-        <v>2924</v>
+        <v>2930</v>
       </c>
       <c r="C1455" t="s" s="2">
-        <v>2925</v>
+        <v>2883</v>
       </c>
       <c r="D1455" s="2"/>
     </row>
@@ -27660,10 +28146,10 @@
         <v>40</v>
       </c>
       <c r="B1456" t="s" s="2">
-        <v>2926</v>
+        <v>2931</v>
       </c>
       <c r="C1456" t="s" s="2">
-        <v>2927</v>
+        <v>2932</v>
       </c>
       <c r="D1456" s="2"/>
     </row>
@@ -27672,10 +28158,10 @@
         <v>40</v>
       </c>
       <c r="B1457" t="s" s="2">
-        <v>2928</v>
+        <v>2933</v>
       </c>
       <c r="C1457" t="s" s="2">
-        <v>2929</v>
+        <v>2934</v>
       </c>
       <c r="D1457" s="2"/>
     </row>
@@ -27684,10 +28170,10 @@
         <v>40</v>
       </c>
       <c r="B1458" t="s" s="2">
-        <v>2930</v>
+        <v>2935</v>
       </c>
       <c r="C1458" t="s" s="2">
-        <v>2931</v>
+        <v>2936</v>
       </c>
       <c r="D1458" s="2"/>
     </row>
@@ -27696,10 +28182,10 @@
         <v>40</v>
       </c>
       <c r="B1459" t="s" s="2">
-        <v>2932</v>
+        <v>2937</v>
       </c>
       <c r="C1459" t="s" s="2">
-        <v>2933</v>
+        <v>2938</v>
       </c>
       <c r="D1459" s="2"/>
     </row>
@@ -27708,10 +28194,10 @@
         <v>40</v>
       </c>
       <c r="B1460" t="s" s="2">
-        <v>2934</v>
+        <v>2939</v>
       </c>
       <c r="C1460" t="s" s="2">
-        <v>2935</v>
+        <v>2940</v>
       </c>
       <c r="D1460" s="2"/>
     </row>
@@ -27720,10 +28206,10 @@
         <v>40</v>
       </c>
       <c r="B1461" t="s" s="2">
-        <v>2936</v>
+        <v>2941</v>
       </c>
       <c r="C1461" t="s" s="2">
-        <v>2937</v>
+        <v>2942</v>
       </c>
       <c r="D1461" s="2"/>
     </row>
@@ -27732,10 +28218,10 @@
         <v>40</v>
       </c>
       <c r="B1462" t="s" s="2">
-        <v>2938</v>
+        <v>2943</v>
       </c>
       <c r="C1462" t="s" s="2">
-        <v>2939</v>
+        <v>2944</v>
       </c>
       <c r="D1462" s="2"/>
     </row>
@@ -27744,10 +28230,10 @@
         <v>40</v>
       </c>
       <c r="B1463" t="s" s="2">
-        <v>2940</v>
+        <v>2945</v>
       </c>
       <c r="C1463" t="s" s="2">
-        <v>2941</v>
+        <v>2946</v>
       </c>
       <c r="D1463" s="2"/>
     </row>
@@ -27756,10 +28242,10 @@
         <v>40</v>
       </c>
       <c r="B1464" t="s" s="2">
-        <v>2942</v>
+        <v>2947</v>
       </c>
       <c r="C1464" t="s" s="2">
-        <v>2943</v>
+        <v>2948</v>
       </c>
       <c r="D1464" s="2"/>
     </row>
@@ -27768,10 +28254,10 @@
         <v>40</v>
       </c>
       <c r="B1465" t="s" s="2">
-        <v>2944</v>
+        <v>2949</v>
       </c>
       <c r="C1465" t="s" s="2">
-        <v>2945</v>
+        <v>2950</v>
       </c>
       <c r="D1465" s="2"/>
     </row>
@@ -27780,10 +28266,10 @@
         <v>40</v>
       </c>
       <c r="B1466" t="s" s="2">
-        <v>2946</v>
+        <v>2951</v>
       </c>
       <c r="C1466" t="s" s="2">
-        <v>2947</v>
+        <v>2952</v>
       </c>
       <c r="D1466" s="2"/>
     </row>
@@ -27792,10 +28278,10 @@
         <v>40</v>
       </c>
       <c r="B1467" t="s" s="2">
-        <v>2948</v>
+        <v>2953</v>
       </c>
       <c r="C1467" t="s" s="2">
-        <v>2949</v>
+        <v>2954</v>
       </c>
       <c r="D1467" s="2"/>
     </row>
@@ -27804,10 +28290,10 @@
         <v>40</v>
       </c>
       <c r="B1468" t="s" s="2">
-        <v>2950</v>
+        <v>2955</v>
       </c>
       <c r="C1468" t="s" s="2">
-        <v>2951</v>
+        <v>2956</v>
       </c>
       <c r="D1468" s="2"/>
     </row>
@@ -27816,10 +28302,10 @@
         <v>40</v>
       </c>
       <c r="B1469" t="s" s="2">
-        <v>2952</v>
+        <v>2957</v>
       </c>
       <c r="C1469" t="s" s="2">
-        <v>2953</v>
+        <v>2958</v>
       </c>
       <c r="D1469" s="2"/>
     </row>
@@ -27828,10 +28314,10 @@
         <v>40</v>
       </c>
       <c r="B1470" t="s" s="2">
-        <v>2954</v>
+        <v>2959</v>
       </c>
       <c r="C1470" t="s" s="2">
-        <v>2955</v>
+        <v>2960</v>
       </c>
       <c r="D1470" s="2"/>
     </row>
@@ -27840,10 +28326,10 @@
         <v>40</v>
       </c>
       <c r="B1471" t="s" s="2">
-        <v>2956</v>
+        <v>2961</v>
       </c>
       <c r="C1471" t="s" s="2">
-        <v>2957</v>
+        <v>2962</v>
       </c>
       <c r="D1471" s="2"/>
     </row>
@@ -27852,10 +28338,10 @@
         <v>40</v>
       </c>
       <c r="B1472" t="s" s="2">
-        <v>2958</v>
+        <v>2963</v>
       </c>
       <c r="C1472" t="s" s="2">
-        <v>2959</v>
+        <v>2964</v>
       </c>
       <c r="D1472" s="2"/>
     </row>
@@ -27864,10 +28350,10 @@
         <v>40</v>
       </c>
       <c r="B1473" t="s" s="2">
-        <v>2960</v>
+        <v>2965</v>
       </c>
       <c r="C1473" t="s" s="2">
-        <v>2961</v>
+        <v>2966</v>
       </c>
       <c r="D1473" s="2"/>
     </row>
@@ -27876,10 +28362,10 @@
         <v>40</v>
       </c>
       <c r="B1474" t="s" s="2">
-        <v>2962</v>
+        <v>2967</v>
       </c>
       <c r="C1474" t="s" s="2">
-        <v>2963</v>
+        <v>2968</v>
       </c>
       <c r="D1474" s="2"/>
     </row>
@@ -27888,10 +28374,10 @@
         <v>40</v>
       </c>
       <c r="B1475" t="s" s="2">
-        <v>2964</v>
+        <v>2969</v>
       </c>
       <c r="C1475" t="s" s="2">
-        <v>2965</v>
+        <v>2970</v>
       </c>
       <c r="D1475" s="2"/>
     </row>
@@ -27900,10 +28386,10 @@
         <v>40</v>
       </c>
       <c r="B1476" t="s" s="2">
-        <v>2966</v>
+        <v>2971</v>
       </c>
       <c r="C1476" t="s" s="2">
-        <v>2967</v>
+        <v>2972</v>
       </c>
       <c r="D1476" s="2"/>
     </row>
@@ -27912,10 +28398,10 @@
         <v>40</v>
       </c>
       <c r="B1477" t="s" s="2">
-        <v>2968</v>
+        <v>2973</v>
       </c>
       <c r="C1477" t="s" s="2">
-        <v>2969</v>
+        <v>2974</v>
       </c>
       <c r="D1477" s="2"/>
     </row>
@@ -27924,10 +28410,10 @@
         <v>40</v>
       </c>
       <c r="B1478" t="s" s="2">
-        <v>2970</v>
+        <v>2975</v>
       </c>
       <c r="C1478" t="s" s="2">
-        <v>2971</v>
+        <v>2976</v>
       </c>
       <c r="D1478" s="2"/>
     </row>
@@ -27936,10 +28422,10 @@
         <v>40</v>
       </c>
       <c r="B1479" t="s" s="2">
-        <v>2972</v>
+        <v>2977</v>
       </c>
       <c r="C1479" t="s" s="2">
-        <v>1687</v>
+        <v>2978</v>
       </c>
       <c r="D1479" s="2"/>
     </row>
@@ -27948,10 +28434,10 @@
         <v>40</v>
       </c>
       <c r="B1480" t="s" s="2">
-        <v>2973</v>
+        <v>2979</v>
       </c>
       <c r="C1480" t="s" s="2">
-        <v>2974</v>
+        <v>2980</v>
       </c>
       <c r="D1480" s="2"/>
     </row>
@@ -27960,10 +28446,10 @@
         <v>40</v>
       </c>
       <c r="B1481" t="s" s="2">
-        <v>2975</v>
+        <v>2981</v>
       </c>
       <c r="C1481" t="s" s="2">
-        <v>2976</v>
+        <v>2982</v>
       </c>
       <c r="D1481" s="2"/>
     </row>
@@ -27972,10 +28458,10 @@
         <v>40</v>
       </c>
       <c r="B1482" t="s" s="2">
-        <v>2977</v>
+        <v>2983</v>
       </c>
       <c r="C1482" t="s" s="2">
-        <v>2978</v>
+        <v>2984</v>
       </c>
       <c r="D1482" s="2"/>
     </row>
@@ -27984,10 +28470,10 @@
         <v>40</v>
       </c>
       <c r="B1483" t="s" s="2">
-        <v>2979</v>
+        <v>2985</v>
       </c>
       <c r="C1483" t="s" s="2">
-        <v>2980</v>
+        <v>2986</v>
       </c>
       <c r="D1483" s="2"/>
     </row>
@@ -27996,10 +28482,10 @@
         <v>40</v>
       </c>
       <c r="B1484" t="s" s="2">
-        <v>2981</v>
+        <v>2987</v>
       </c>
       <c r="C1484" t="s" s="2">
-        <v>2982</v>
+        <v>2988</v>
       </c>
       <c r="D1484" s="2"/>
     </row>
@@ -28008,10 +28494,10 @@
         <v>40</v>
       </c>
       <c r="B1485" t="s" s="2">
-        <v>2983</v>
+        <v>2989</v>
       </c>
       <c r="C1485" t="s" s="2">
-        <v>2984</v>
+        <v>2990</v>
       </c>
       <c r="D1485" s="2"/>
     </row>
@@ -28020,10 +28506,10 @@
         <v>40</v>
       </c>
       <c r="B1486" t="s" s="2">
-        <v>2985</v>
+        <v>2991</v>
       </c>
       <c r="C1486" t="s" s="2">
-        <v>2986</v>
+        <v>2992</v>
       </c>
       <c r="D1486" s="2"/>
     </row>
@@ -28032,10 +28518,10 @@
         <v>40</v>
       </c>
       <c r="B1487" t="s" s="2">
-        <v>2987</v>
+        <v>2993</v>
       </c>
       <c r="C1487" t="s" s="2">
-        <v>2988</v>
+        <v>2994</v>
       </c>
       <c r="D1487" s="2"/>
     </row>
@@ -28044,10 +28530,10 @@
         <v>40</v>
       </c>
       <c r="B1488" t="s" s="2">
-        <v>2989</v>
+        <v>2995</v>
       </c>
       <c r="C1488" t="s" s="2">
-        <v>2990</v>
+        <v>2996</v>
       </c>
       <c r="D1488" s="2"/>
     </row>
@@ -28056,10 +28542,10 @@
         <v>40</v>
       </c>
       <c r="B1489" t="s" s="2">
-        <v>2991</v>
+        <v>2997</v>
       </c>
       <c r="C1489" t="s" s="2">
-        <v>2992</v>
+        <v>2998</v>
       </c>
       <c r="D1489" s="2"/>
     </row>
@@ -28068,10 +28554,10 @@
         <v>40</v>
       </c>
       <c r="B1490" t="s" s="2">
-        <v>2993</v>
+        <v>2999</v>
       </c>
       <c r="C1490" t="s" s="2">
-        <v>2994</v>
+        <v>3000</v>
       </c>
       <c r="D1490" s="2"/>
     </row>
@@ -28080,10 +28566,10 @@
         <v>40</v>
       </c>
       <c r="B1491" t="s" s="2">
-        <v>2995</v>
+        <v>3001</v>
       </c>
       <c r="C1491" t="s" s="2">
-        <v>2996</v>
+        <v>3002</v>
       </c>
       <c r="D1491" s="2"/>
     </row>
@@ -28092,10 +28578,10 @@
         <v>40</v>
       </c>
       <c r="B1492" t="s" s="2">
-        <v>2997</v>
+        <v>3003</v>
       </c>
       <c r="C1492" t="s" s="2">
-        <v>2998</v>
+        <v>3004</v>
       </c>
       <c r="D1492" s="2"/>
     </row>
@@ -28104,10 +28590,10 @@
         <v>40</v>
       </c>
       <c r="B1493" t="s" s="2">
-        <v>2999</v>
+        <v>3005</v>
       </c>
       <c r="C1493" t="s" s="2">
-        <v>3000</v>
+        <v>327</v>
       </c>
       <c r="D1493" s="2"/>
     </row>
@@ -28116,10 +28602,10 @@
         <v>40</v>
       </c>
       <c r="B1494" t="s" s="2">
-        <v>3001</v>
+        <v>3006</v>
       </c>
       <c r="C1494" t="s" s="2">
-        <v>3002</v>
+        <v>3007</v>
       </c>
       <c r="D1494" s="2"/>
     </row>
@@ -28128,10 +28614,10 @@
         <v>40</v>
       </c>
       <c r="B1495" t="s" s="2">
-        <v>3003</v>
+        <v>3008</v>
       </c>
       <c r="C1495" t="s" s="2">
-        <v>3004</v>
+        <v>3009</v>
       </c>
       <c r="D1495" s="2"/>
     </row>
@@ -28140,10 +28626,10 @@
         <v>40</v>
       </c>
       <c r="B1496" t="s" s="2">
-        <v>3005</v>
+        <v>3010</v>
       </c>
       <c r="C1496" t="s" s="2">
-        <v>3006</v>
+        <v>3011</v>
       </c>
       <c r="D1496" s="2"/>
     </row>
@@ -28152,10 +28638,10 @@
         <v>40</v>
       </c>
       <c r="B1497" t="s" s="2">
-        <v>3007</v>
+        <v>3012</v>
       </c>
       <c r="C1497" t="s" s="2">
-        <v>3008</v>
+        <v>3013</v>
       </c>
       <c r="D1497" s="2"/>
     </row>
@@ -28164,10 +28650,10 @@
         <v>40</v>
       </c>
       <c r="B1498" t="s" s="2">
-        <v>3009</v>
+        <v>3014</v>
       </c>
       <c r="C1498" t="s" s="2">
-        <v>3010</v>
+        <v>3015</v>
       </c>
       <c r="D1498" s="2"/>
     </row>
@@ -28176,10 +28662,10 @@
         <v>40</v>
       </c>
       <c r="B1499" t="s" s="2">
-        <v>3011</v>
+        <v>3016</v>
       </c>
       <c r="C1499" t="s" s="2">
-        <v>3012</v>
+        <v>3017</v>
       </c>
       <c r="D1499" s="2"/>
     </row>
@@ -28188,10 +28674,10 @@
         <v>40</v>
       </c>
       <c r="B1500" t="s" s="2">
-        <v>3013</v>
+        <v>3018</v>
       </c>
       <c r="C1500" t="s" s="2">
-        <v>3014</v>
+        <v>3019</v>
       </c>
       <c r="D1500" s="2"/>
     </row>
@@ -28200,10 +28686,10 @@
         <v>40</v>
       </c>
       <c r="B1501" t="s" s="2">
-        <v>3015</v>
+        <v>3020</v>
       </c>
       <c r="C1501" t="s" s="2">
-        <v>3016</v>
+        <v>3021</v>
       </c>
       <c r="D1501" s="2"/>
     </row>
@@ -28212,10 +28698,10 @@
         <v>40</v>
       </c>
       <c r="B1502" t="s" s="2">
-        <v>3017</v>
+        <v>3022</v>
       </c>
       <c r="C1502" t="s" s="2">
-        <v>3018</v>
+        <v>3023</v>
       </c>
       <c r="D1502" s="2"/>
     </row>
@@ -28224,10 +28710,10 @@
         <v>40</v>
       </c>
       <c r="B1503" t="s" s="2">
-        <v>3019</v>
+        <v>3024</v>
       </c>
       <c r="C1503" t="s" s="2">
-        <v>3020</v>
+        <v>3025</v>
       </c>
       <c r="D1503" s="2"/>
     </row>
@@ -28236,10 +28722,10 @@
         <v>40</v>
       </c>
       <c r="B1504" t="s" s="2">
-        <v>3021</v>
+        <v>3026</v>
       </c>
       <c r="C1504" t="s" s="2">
-        <v>3022</v>
+        <v>3027</v>
       </c>
       <c r="D1504" s="2"/>
     </row>
@@ -28248,10 +28734,10 @@
         <v>40</v>
       </c>
       <c r="B1505" t="s" s="2">
-        <v>3023</v>
+        <v>3028</v>
       </c>
       <c r="C1505" t="s" s="2">
-        <v>3024</v>
+        <v>3029</v>
       </c>
       <c r="D1505" s="2"/>
     </row>
@@ -28260,10 +28746,10 @@
         <v>40</v>
       </c>
       <c r="B1506" t="s" s="2">
-        <v>3025</v>
+        <v>3030</v>
       </c>
       <c r="C1506" t="s" s="2">
-        <v>3026</v>
+        <v>3031</v>
       </c>
       <c r="D1506" s="2"/>
     </row>
@@ -28272,10 +28758,10 @@
         <v>40</v>
       </c>
       <c r="B1507" t="s" s="2">
-        <v>3027</v>
+        <v>3032</v>
       </c>
       <c r="C1507" t="s" s="2">
-        <v>3028</v>
+        <v>3033</v>
       </c>
       <c r="D1507" s="2"/>
     </row>
@@ -28284,10 +28770,10 @@
         <v>40</v>
       </c>
       <c r="B1508" t="s" s="2">
-        <v>3029</v>
+        <v>3034</v>
       </c>
       <c r="C1508" t="s" s="2">
-        <v>3030</v>
+        <v>3035</v>
       </c>
       <c r="D1508" s="2"/>
     </row>
@@ -28296,10 +28782,10 @@
         <v>40</v>
       </c>
       <c r="B1509" t="s" s="2">
-        <v>3031</v>
+        <v>3036</v>
       </c>
       <c r="C1509" t="s" s="2">
-        <v>3032</v>
+        <v>3037</v>
       </c>
       <c r="D1509" s="2"/>
     </row>
@@ -28308,10 +28794,10 @@
         <v>40</v>
       </c>
       <c r="B1510" t="s" s="2">
-        <v>3033</v>
+        <v>3038</v>
       </c>
       <c r="C1510" t="s" s="2">
-        <v>3034</v>
+        <v>3039</v>
       </c>
       <c r="D1510" s="2"/>
     </row>
@@ -28320,10 +28806,10 @@
         <v>40</v>
       </c>
       <c r="B1511" t="s" s="2">
-        <v>3035</v>
+        <v>3040</v>
       </c>
       <c r="C1511" t="s" s="2">
-        <v>3036</v>
+        <v>3041</v>
       </c>
       <c r="D1511" s="2"/>
     </row>
@@ -28332,10 +28818,10 @@
         <v>40</v>
       </c>
       <c r="B1512" t="s" s="2">
-        <v>3037</v>
+        <v>3042</v>
       </c>
       <c r="C1512" t="s" s="2">
-        <v>3038</v>
+        <v>3043</v>
       </c>
       <c r="D1512" s="2"/>
     </row>
@@ -28344,10 +28830,10 @@
         <v>40</v>
       </c>
       <c r="B1513" t="s" s="2">
-        <v>3039</v>
+        <v>3044</v>
       </c>
       <c r="C1513" t="s" s="2">
-        <v>3040</v>
+        <v>3045</v>
       </c>
       <c r="D1513" s="2"/>
     </row>
@@ -28356,10 +28842,10 @@
         <v>40</v>
       </c>
       <c r="B1514" t="s" s="2">
-        <v>3041</v>
+        <v>3046</v>
       </c>
       <c r="C1514" t="s" s="2">
-        <v>3042</v>
+        <v>3047</v>
       </c>
       <c r="D1514" s="2"/>
     </row>
@@ -28368,10 +28854,10 @@
         <v>40</v>
       </c>
       <c r="B1515" t="s" s="2">
-        <v>3043</v>
+        <v>3048</v>
       </c>
       <c r="C1515" t="s" s="2">
-        <v>3044</v>
+        <v>3049</v>
       </c>
       <c r="D1515" s="2"/>
     </row>
@@ -28380,10 +28866,10 @@
         <v>40</v>
       </c>
       <c r="B1516" t="s" s="2">
-        <v>3045</v>
+        <v>3050</v>
       </c>
       <c r="C1516" t="s" s="2">
-        <v>3046</v>
+        <v>3051</v>
       </c>
       <c r="D1516" s="2"/>
     </row>
@@ -28392,10 +28878,10 @@
         <v>40</v>
       </c>
       <c r="B1517" t="s" s="2">
-        <v>3047</v>
+        <v>3052</v>
       </c>
       <c r="C1517" t="s" s="2">
-        <v>3048</v>
+        <v>3053</v>
       </c>
       <c r="D1517" s="2"/>
     </row>
@@ -28404,10 +28890,10 @@
         <v>40</v>
       </c>
       <c r="B1518" t="s" s="2">
-        <v>3049</v>
+        <v>3054</v>
       </c>
       <c r="C1518" t="s" s="2">
-        <v>3050</v>
+        <v>3055</v>
       </c>
       <c r="D1518" s="2"/>
     </row>
@@ -28416,10 +28902,10 @@
         <v>40</v>
       </c>
       <c r="B1519" t="s" s="2">
-        <v>3051</v>
+        <v>3056</v>
       </c>
       <c r="C1519" t="s" s="2">
-        <v>3052</v>
+        <v>3057</v>
       </c>
       <c r="D1519" s="2"/>
     </row>
@@ -28428,10 +28914,10 @@
         <v>40</v>
       </c>
       <c r="B1520" t="s" s="2">
-        <v>3053</v>
+        <v>3058</v>
       </c>
       <c r="C1520" t="s" s="2">
-        <v>3054</v>
+        <v>3059</v>
       </c>
       <c r="D1520" s="2"/>
     </row>
@@ -28440,10 +28926,10 @@
         <v>40</v>
       </c>
       <c r="B1521" t="s" s="2">
-        <v>3055</v>
+        <v>3060</v>
       </c>
       <c r="C1521" t="s" s="2">
-        <v>3056</v>
+        <v>3061</v>
       </c>
       <c r="D1521" s="2"/>
     </row>
@@ -28452,10 +28938,10 @@
         <v>40</v>
       </c>
       <c r="B1522" t="s" s="2">
-        <v>3057</v>
+        <v>3062</v>
       </c>
       <c r="C1522" t="s" s="2">
-        <v>3058</v>
+        <v>3063</v>
       </c>
       <c r="D1522" s="2"/>
     </row>
@@ -28464,10 +28950,10 @@
         <v>40</v>
       </c>
       <c r="B1523" t="s" s="2">
-        <v>3059</v>
+        <v>3064</v>
       </c>
       <c r="C1523" t="s" s="2">
-        <v>3060</v>
+        <v>3065</v>
       </c>
       <c r="D1523" s="2"/>
     </row>
@@ -28476,10 +28962,10 @@
         <v>40</v>
       </c>
       <c r="B1524" t="s" s="2">
-        <v>3061</v>
+        <v>3066</v>
       </c>
       <c r="C1524" t="s" s="2">
-        <v>3062</v>
+        <v>3067</v>
       </c>
       <c r="D1524" s="2"/>
     </row>
@@ -28488,10 +28974,10 @@
         <v>40</v>
       </c>
       <c r="B1525" t="s" s="2">
-        <v>3063</v>
+        <v>3068</v>
       </c>
       <c r="C1525" t="s" s="2">
-        <v>3064</v>
+        <v>3069</v>
       </c>
       <c r="D1525" s="2"/>
     </row>
@@ -28500,10 +28986,10 @@
         <v>40</v>
       </c>
       <c r="B1526" t="s" s="2">
-        <v>3065</v>
+        <v>3070</v>
       </c>
       <c r="C1526" t="s" s="2">
-        <v>3066</v>
+        <v>3071</v>
       </c>
       <c r="D1526" s="2"/>
     </row>
@@ -28512,10 +28998,10 @@
         <v>40</v>
       </c>
       <c r="B1527" t="s" s="2">
-        <v>3067</v>
+        <v>3072</v>
       </c>
       <c r="C1527" t="s" s="2">
-        <v>3068</v>
+        <v>3073</v>
       </c>
       <c r="D1527" s="2"/>
     </row>
@@ -28524,10 +29010,10 @@
         <v>40</v>
       </c>
       <c r="B1528" t="s" s="2">
-        <v>3069</v>
+        <v>3074</v>
       </c>
       <c r="C1528" t="s" s="2">
-        <v>3070</v>
+        <v>3075</v>
       </c>
       <c r="D1528" s="2"/>
     </row>
@@ -28536,10 +29022,10 @@
         <v>40</v>
       </c>
       <c r="B1529" t="s" s="2">
-        <v>3071</v>
+        <v>3076</v>
       </c>
       <c r="C1529" t="s" s="2">
-        <v>3072</v>
+        <v>3077</v>
       </c>
       <c r="D1529" s="2"/>
     </row>
@@ -28548,10 +29034,10 @@
         <v>40</v>
       </c>
       <c r="B1530" t="s" s="2">
-        <v>3073</v>
+        <v>3078</v>
       </c>
       <c r="C1530" t="s" s="2">
-        <v>3074</v>
+        <v>3079</v>
       </c>
       <c r="D1530" s="2"/>
     </row>
@@ -28560,10 +29046,10 @@
         <v>40</v>
       </c>
       <c r="B1531" t="s" s="2">
-        <v>3075</v>
+        <v>3080</v>
       </c>
       <c r="C1531" t="s" s="2">
-        <v>3076</v>
+        <v>3081</v>
       </c>
       <c r="D1531" s="2"/>
     </row>
@@ -28572,10 +29058,10 @@
         <v>40</v>
       </c>
       <c r="B1532" t="s" s="2">
-        <v>3077</v>
+        <v>3082</v>
       </c>
       <c r="C1532" t="s" s="2">
-        <v>3078</v>
+        <v>3083</v>
       </c>
       <c r="D1532" s="2"/>
     </row>
@@ -28584,10 +29070,10 @@
         <v>40</v>
       </c>
       <c r="B1533" t="s" s="2">
-        <v>3079</v>
+        <v>3084</v>
       </c>
       <c r="C1533" t="s" s="2">
-        <v>3080</v>
+        <v>3085</v>
       </c>
       <c r="D1533" s="2"/>
     </row>
@@ -28596,10 +29082,10 @@
         <v>40</v>
       </c>
       <c r="B1534" t="s" s="2">
-        <v>3081</v>
+        <v>3086</v>
       </c>
       <c r="C1534" t="s" s="2">
-        <v>3082</v>
+        <v>3087</v>
       </c>
       <c r="D1534" s="2"/>
     </row>
@@ -28608,10 +29094,10 @@
         <v>40</v>
       </c>
       <c r="B1535" t="s" s="2">
-        <v>3083</v>
+        <v>3088</v>
       </c>
       <c r="C1535" t="s" s="2">
-        <v>3084</v>
+        <v>3089</v>
       </c>
       <c r="D1535" s="2"/>
     </row>
@@ -28620,10 +29106,10 @@
         <v>40</v>
       </c>
       <c r="B1536" t="s" s="2">
-        <v>3085</v>
+        <v>3090</v>
       </c>
       <c r="C1536" t="s" s="2">
-        <v>3086</v>
+        <v>3091</v>
       </c>
       <c r="D1536" s="2"/>
     </row>
@@ -28632,10 +29118,10 @@
         <v>40</v>
       </c>
       <c r="B1537" t="s" s="2">
-        <v>3087</v>
+        <v>3092</v>
       </c>
       <c r="C1537" t="s" s="2">
-        <v>3088</v>
+        <v>3093</v>
       </c>
       <c r="D1537" s="2"/>
     </row>
@@ -28644,10 +29130,10 @@
         <v>40</v>
       </c>
       <c r="B1538" t="s" s="2">
-        <v>3089</v>
+        <v>3094</v>
       </c>
       <c r="C1538" t="s" s="2">
-        <v>3090</v>
+        <v>3095</v>
       </c>
       <c r="D1538" s="2"/>
     </row>
@@ -28656,10 +29142,10 @@
         <v>40</v>
       </c>
       <c r="B1539" t="s" s="2">
-        <v>3091</v>
+        <v>3096</v>
       </c>
       <c r="C1539" t="s" s="2">
-        <v>3092</v>
+        <v>1773</v>
       </c>
       <c r="D1539" s="2"/>
     </row>
@@ -28668,10 +29154,10 @@
         <v>40</v>
       </c>
       <c r="B1540" t="s" s="2">
-        <v>3093</v>
+        <v>3097</v>
       </c>
       <c r="C1540" t="s" s="2">
-        <v>3094</v>
+        <v>3098</v>
       </c>
       <c r="D1540" s="2"/>
     </row>
@@ -28680,10 +29166,10 @@
         <v>40</v>
       </c>
       <c r="B1541" t="s" s="2">
-        <v>3095</v>
+        <v>3099</v>
       </c>
       <c r="C1541" t="s" s="2">
-        <v>3096</v>
+        <v>3100</v>
       </c>
       <c r="D1541" s="2"/>
     </row>
@@ -28692,10 +29178,10 @@
         <v>40</v>
       </c>
       <c r="B1542" t="s" s="2">
-        <v>3097</v>
+        <v>3101</v>
       </c>
       <c r="C1542" t="s" s="2">
-        <v>3098</v>
+        <v>3102</v>
       </c>
       <c r="D1542" s="2"/>
     </row>
@@ -28704,10 +29190,10 @@
         <v>40</v>
       </c>
       <c r="B1543" t="s" s="2">
-        <v>3099</v>
+        <v>3103</v>
       </c>
       <c r="C1543" t="s" s="2">
-        <v>3100</v>
+        <v>3104</v>
       </c>
       <c r="D1543" s="2"/>
     </row>
@@ -28716,10 +29202,10 @@
         <v>40</v>
       </c>
       <c r="B1544" t="s" s="2">
-        <v>3101</v>
+        <v>3105</v>
       </c>
       <c r="C1544" t="s" s="2">
-        <v>3102</v>
+        <v>3106</v>
       </c>
       <c r="D1544" s="2"/>
     </row>
@@ -28728,10 +29214,10 @@
         <v>40</v>
       </c>
       <c r="B1545" t="s" s="2">
-        <v>3103</v>
+        <v>3107</v>
       </c>
       <c r="C1545" t="s" s="2">
-        <v>3104</v>
+        <v>3108</v>
       </c>
       <c r="D1545" s="2"/>
     </row>
@@ -28740,10 +29226,10 @@
         <v>40</v>
       </c>
       <c r="B1546" t="s" s="2">
-        <v>3105</v>
+        <v>3109</v>
       </c>
       <c r="C1546" t="s" s="2">
-        <v>3106</v>
+        <v>3110</v>
       </c>
       <c r="D1546" s="2"/>
     </row>
@@ -28752,10 +29238,10 @@
         <v>40</v>
       </c>
       <c r="B1547" t="s" s="2">
-        <v>3107</v>
+        <v>3111</v>
       </c>
       <c r="C1547" t="s" s="2">
-        <v>3108</v>
+        <v>3112</v>
       </c>
       <c r="D1547" s="2"/>
     </row>
@@ -28764,10 +29250,10 @@
         <v>40</v>
       </c>
       <c r="B1548" t="s" s="2">
-        <v>3109</v>
+        <v>3113</v>
       </c>
       <c r="C1548" t="s" s="2">
-        <v>3110</v>
+        <v>3114</v>
       </c>
       <c r="D1548" s="2"/>
     </row>
@@ -28776,10 +29262,10 @@
         <v>40</v>
       </c>
       <c r="B1549" t="s" s="2">
-        <v>3111</v>
+        <v>3115</v>
       </c>
       <c r="C1549" t="s" s="2">
-        <v>3112</v>
+        <v>3116</v>
       </c>
       <c r="D1549" s="2"/>
     </row>
@@ -28788,10 +29274,10 @@
         <v>40</v>
       </c>
       <c r="B1550" t="s" s="2">
-        <v>3113</v>
+        <v>3117</v>
       </c>
       <c r="C1550" t="s" s="2">
-        <v>3114</v>
+        <v>3118</v>
       </c>
       <c r="D1550" s="2"/>
     </row>
@@ -28800,10 +29286,10 @@
         <v>40</v>
       </c>
       <c r="B1551" t="s" s="2">
-        <v>3115</v>
+        <v>3119</v>
       </c>
       <c r="C1551" t="s" s="2">
-        <v>3116</v>
+        <v>3120</v>
       </c>
       <c r="D1551" s="2"/>
     </row>
@@ -28812,10 +29298,10 @@
         <v>40</v>
       </c>
       <c r="B1552" t="s" s="2">
-        <v>3117</v>
+        <v>3121</v>
       </c>
       <c r="C1552" t="s" s="2">
-        <v>3118</v>
+        <v>3122</v>
       </c>
       <c r="D1552" s="2"/>
     </row>
@@ -28824,10 +29310,10 @@
         <v>40</v>
       </c>
       <c r="B1553" t="s" s="2">
-        <v>3119</v>
+        <v>3123</v>
       </c>
       <c r="C1553" t="s" s="2">
-        <v>3120</v>
+        <v>3124</v>
       </c>
       <c r="D1553" s="2"/>
     </row>
@@ -28836,10 +29322,10 @@
         <v>40</v>
       </c>
       <c r="B1554" t="s" s="2">
-        <v>3121</v>
+        <v>3125</v>
       </c>
       <c r="C1554" t="s" s="2">
-        <v>3122</v>
+        <v>3126</v>
       </c>
       <c r="D1554" s="2"/>
     </row>
@@ -28848,10 +29334,10 @@
         <v>40</v>
       </c>
       <c r="B1555" t="s" s="2">
-        <v>3123</v>
+        <v>3127</v>
       </c>
       <c r="C1555" t="s" s="2">
-        <v>3124</v>
+        <v>3128</v>
       </c>
       <c r="D1555" s="2"/>
     </row>
@@ -28860,10 +29346,10 @@
         <v>40</v>
       </c>
       <c r="B1556" t="s" s="2">
-        <v>3125</v>
+        <v>3129</v>
       </c>
       <c r="C1556" t="s" s="2">
-        <v>3126</v>
+        <v>3130</v>
       </c>
       <c r="D1556" s="2"/>
     </row>
@@ -28872,10 +29358,10 @@
         <v>40</v>
       </c>
       <c r="B1557" t="s" s="2">
-        <v>3127</v>
+        <v>3131</v>
       </c>
       <c r="C1557" t="s" s="2">
-        <v>3128</v>
+        <v>3132</v>
       </c>
       <c r="D1557" s="2"/>
     </row>
@@ -28884,10 +29370,10 @@
         <v>40</v>
       </c>
       <c r="B1558" t="s" s="2">
-        <v>3129</v>
+        <v>3133</v>
       </c>
       <c r="C1558" t="s" s="2">
-        <v>3130</v>
+        <v>3134</v>
       </c>
       <c r="D1558" s="2"/>
     </row>
@@ -28896,10 +29382,10 @@
         <v>40</v>
       </c>
       <c r="B1559" t="s" s="2">
-        <v>3131</v>
+        <v>3135</v>
       </c>
       <c r="C1559" t="s" s="2">
-        <v>3132</v>
+        <v>3136</v>
       </c>
       <c r="D1559" s="2"/>
     </row>
@@ -28908,10 +29394,10 @@
         <v>40</v>
       </c>
       <c r="B1560" t="s" s="2">
-        <v>3133</v>
+        <v>3137</v>
       </c>
       <c r="C1560" t="s" s="2">
-        <v>3134</v>
+        <v>3138</v>
       </c>
       <c r="D1560" s="2"/>
     </row>
@@ -28920,10 +29406,10 @@
         <v>40</v>
       </c>
       <c r="B1561" t="s" s="2">
-        <v>3135</v>
+        <v>3139</v>
       </c>
       <c r="C1561" t="s" s="2">
-        <v>3136</v>
+        <v>3140</v>
       </c>
       <c r="D1561" s="2"/>
     </row>
@@ -28932,10 +29418,10 @@
         <v>40</v>
       </c>
       <c r="B1562" t="s" s="2">
-        <v>3137</v>
+        <v>3141</v>
       </c>
       <c r="C1562" t="s" s="2">
-        <v>3138</v>
+        <v>3142</v>
       </c>
       <c r="D1562" s="2"/>
     </row>
@@ -28944,10 +29430,10 @@
         <v>40</v>
       </c>
       <c r="B1563" t="s" s="2">
-        <v>3139</v>
+        <v>3143</v>
       </c>
       <c r="C1563" t="s" s="2">
-        <v>3140</v>
+        <v>3144</v>
       </c>
       <c r="D1563" s="2"/>
     </row>
@@ -28956,10 +29442,10 @@
         <v>40</v>
       </c>
       <c r="B1564" t="s" s="2">
-        <v>3141</v>
+        <v>3145</v>
       </c>
       <c r="C1564" t="s" s="2">
-        <v>3142</v>
+        <v>3146</v>
       </c>
       <c r="D1564" s="2"/>
     </row>
@@ -28968,10 +29454,10 @@
         <v>40</v>
       </c>
       <c r="B1565" t="s" s="2">
-        <v>3143</v>
+        <v>3147</v>
       </c>
       <c r="C1565" t="s" s="2">
-        <v>3144</v>
+        <v>3148</v>
       </c>
       <c r="D1565" s="2"/>
     </row>
@@ -28980,10 +29466,10 @@
         <v>40</v>
       </c>
       <c r="B1566" t="s" s="2">
-        <v>3145</v>
+        <v>3149</v>
       </c>
       <c r="C1566" t="s" s="2">
-        <v>3146</v>
+        <v>3150</v>
       </c>
       <c r="D1566" s="2"/>
     </row>
@@ -28992,10 +29478,10 @@
         <v>40</v>
       </c>
       <c r="B1567" t="s" s="2">
-        <v>3147</v>
+        <v>3151</v>
       </c>
       <c r="C1567" t="s" s="2">
-        <v>3148</v>
+        <v>3152</v>
       </c>
       <c r="D1567" s="2"/>
     </row>
@@ -29004,10 +29490,10 @@
         <v>40</v>
       </c>
       <c r="B1568" t="s" s="2">
-        <v>3149</v>
+        <v>3153</v>
       </c>
       <c r="C1568" t="s" s="2">
-        <v>3150</v>
+        <v>3154</v>
       </c>
       <c r="D1568" s="2"/>
     </row>
@@ -29016,10 +29502,10 @@
         <v>40</v>
       </c>
       <c r="B1569" t="s" s="2">
-        <v>3151</v>
+        <v>3155</v>
       </c>
       <c r="C1569" t="s" s="2">
-        <v>3152</v>
+        <v>3156</v>
       </c>
       <c r="D1569" s="2"/>
     </row>
@@ -29028,10 +29514,10 @@
         <v>40</v>
       </c>
       <c r="B1570" t="s" s="2">
-        <v>3153</v>
+        <v>3157</v>
       </c>
       <c r="C1570" t="s" s="2">
-        <v>2978</v>
+        <v>3158</v>
       </c>
       <c r="D1570" s="2"/>
     </row>
@@ -29040,10 +29526,10 @@
         <v>40</v>
       </c>
       <c r="B1571" t="s" s="2">
-        <v>3154</v>
+        <v>3159</v>
       </c>
       <c r="C1571" t="s" s="2">
-        <v>3155</v>
+        <v>3160</v>
       </c>
       <c r="D1571" s="2"/>
     </row>
@@ -29052,10 +29538,10 @@
         <v>40</v>
       </c>
       <c r="B1572" t="s" s="2">
-        <v>3156</v>
+        <v>3161</v>
       </c>
       <c r="C1572" t="s" s="2">
-        <v>3157</v>
+        <v>3162</v>
       </c>
       <c r="D1572" s="2"/>
     </row>
@@ -29064,10 +29550,10 @@
         <v>40</v>
       </c>
       <c r="B1573" t="s" s="2">
-        <v>3158</v>
+        <v>3163</v>
       </c>
       <c r="C1573" t="s" s="2">
-        <v>3159</v>
+        <v>3164</v>
       </c>
       <c r="D1573" s="2"/>
     </row>
@@ -29076,10 +29562,10 @@
         <v>40</v>
       </c>
       <c r="B1574" t="s" s="2">
-        <v>3160</v>
+        <v>3165</v>
       </c>
       <c r="C1574" t="s" s="2">
-        <v>3161</v>
+        <v>3166</v>
       </c>
       <c r="D1574" s="2"/>
     </row>
@@ -29088,10 +29574,10 @@
         <v>40</v>
       </c>
       <c r="B1575" t="s" s="2">
-        <v>3162</v>
+        <v>3167</v>
       </c>
       <c r="C1575" t="s" s="2">
-        <v>3163</v>
+        <v>3168</v>
       </c>
       <c r="D1575" s="2"/>
     </row>
@@ -29100,10 +29586,10 @@
         <v>40</v>
       </c>
       <c r="B1576" t="s" s="2">
-        <v>3164</v>
+        <v>3169</v>
       </c>
       <c r="C1576" t="s" s="2">
-        <v>3165</v>
+        <v>3170</v>
       </c>
       <c r="D1576" s="2"/>
     </row>
@@ -29112,10 +29598,10 @@
         <v>40</v>
       </c>
       <c r="B1577" t="s" s="2">
-        <v>3166</v>
+        <v>3171</v>
       </c>
       <c r="C1577" t="s" s="2">
-        <v>3167</v>
+        <v>3172</v>
       </c>
       <c r="D1577" s="2"/>
     </row>
@@ -29124,10 +29610,10 @@
         <v>40</v>
       </c>
       <c r="B1578" t="s" s="2">
-        <v>3168</v>
+        <v>3173</v>
       </c>
       <c r="C1578" t="s" s="2">
-        <v>3169</v>
+        <v>3174</v>
       </c>
       <c r="D1578" s="2"/>
     </row>
@@ -29136,10 +29622,10 @@
         <v>40</v>
       </c>
       <c r="B1579" t="s" s="2">
-        <v>3170</v>
+        <v>3175</v>
       </c>
       <c r="C1579" t="s" s="2">
-        <v>3171</v>
+        <v>3176</v>
       </c>
       <c r="D1579" s="2"/>
     </row>
@@ -29148,10 +29634,10 @@
         <v>40</v>
       </c>
       <c r="B1580" t="s" s="2">
-        <v>3172</v>
+        <v>3177</v>
       </c>
       <c r="C1580" t="s" s="2">
-        <v>3173</v>
+        <v>3178</v>
       </c>
       <c r="D1580" s="2"/>
     </row>
@@ -29160,10 +29646,10 @@
         <v>40</v>
       </c>
       <c r="B1581" t="s" s="2">
-        <v>3174</v>
+        <v>3179</v>
       </c>
       <c r="C1581" t="s" s="2">
-        <v>3175</v>
+        <v>3180</v>
       </c>
       <c r="D1581" s="2"/>
     </row>
@@ -29172,10 +29658,10 @@
         <v>40</v>
       </c>
       <c r="B1582" t="s" s="2">
-        <v>3176</v>
+        <v>3181</v>
       </c>
       <c r="C1582" t="s" s="2">
-        <v>3177</v>
+        <v>3182</v>
       </c>
       <c r="D1582" s="2"/>
     </row>
@@ -29184,10 +29670,10 @@
         <v>40</v>
       </c>
       <c r="B1583" t="s" s="2">
-        <v>3178</v>
+        <v>3183</v>
       </c>
       <c r="C1583" t="s" s="2">
-        <v>3179</v>
+        <v>3184</v>
       </c>
       <c r="D1583" s="2"/>
     </row>
@@ -29196,10 +29682,10 @@
         <v>40</v>
       </c>
       <c r="B1584" t="s" s="2">
-        <v>3180</v>
+        <v>3185</v>
       </c>
       <c r="C1584" t="s" s="2">
-        <v>3181</v>
+        <v>3186</v>
       </c>
       <c r="D1584" s="2"/>
     </row>
@@ -29208,10 +29694,10 @@
         <v>40</v>
       </c>
       <c r="B1585" t="s" s="2">
-        <v>3182</v>
+        <v>3187</v>
       </c>
       <c r="C1585" t="s" s="2">
-        <v>3183</v>
+        <v>3188</v>
       </c>
       <c r="D1585" s="2"/>
     </row>
@@ -29220,10 +29706,10 @@
         <v>40</v>
       </c>
       <c r="B1586" t="s" s="2">
-        <v>3184</v>
+        <v>3189</v>
       </c>
       <c r="C1586" t="s" s="2">
-        <v>3185</v>
+        <v>3190</v>
       </c>
       <c r="D1586" s="2"/>
     </row>
@@ -29232,10 +29718,10 @@
         <v>40</v>
       </c>
       <c r="B1587" t="s" s="2">
-        <v>3186</v>
+        <v>3191</v>
       </c>
       <c r="C1587" t="s" s="2">
-        <v>3187</v>
+        <v>3192</v>
       </c>
       <c r="D1587" s="2"/>
     </row>
@@ -29244,10 +29730,10 @@
         <v>40</v>
       </c>
       <c r="B1588" t="s" s="2">
-        <v>3188</v>
+        <v>3193</v>
       </c>
       <c r="C1588" t="s" s="2">
-        <v>3189</v>
+        <v>3194</v>
       </c>
       <c r="D1588" s="2"/>
     </row>
@@ -29256,10 +29742,10 @@
         <v>40</v>
       </c>
       <c r="B1589" t="s" s="2">
-        <v>3190</v>
+        <v>3195</v>
       </c>
       <c r="C1589" t="s" s="2">
-        <v>3191</v>
+        <v>3196</v>
       </c>
       <c r="D1589" s="2"/>
     </row>
@@ -29268,10 +29754,10 @@
         <v>40</v>
       </c>
       <c r="B1590" t="s" s="2">
-        <v>3192</v>
+        <v>3197</v>
       </c>
       <c r="C1590" t="s" s="2">
-        <v>3193</v>
+        <v>3198</v>
       </c>
       <c r="D1590" s="2"/>
     </row>
@@ -29280,10 +29766,10 @@
         <v>40</v>
       </c>
       <c r="B1591" t="s" s="2">
-        <v>3194</v>
+        <v>3199</v>
       </c>
       <c r="C1591" t="s" s="2">
-        <v>3195</v>
+        <v>3200</v>
       </c>
       <c r="D1591" s="2"/>
     </row>
@@ -29292,10 +29778,10 @@
         <v>40</v>
       </c>
       <c r="B1592" t="s" s="2">
-        <v>3196</v>
+        <v>3201</v>
       </c>
       <c r="C1592" t="s" s="2">
-        <v>3197</v>
+        <v>3202</v>
       </c>
       <c r="D1592" s="2"/>
     </row>
@@ -29304,10 +29790,10 @@
         <v>40</v>
       </c>
       <c r="B1593" t="s" s="2">
-        <v>3198</v>
+        <v>3203</v>
       </c>
       <c r="C1593" t="s" s="2">
-        <v>3199</v>
+        <v>3204</v>
       </c>
       <c r="D1593" s="2"/>
     </row>
@@ -29316,10 +29802,10 @@
         <v>40</v>
       </c>
       <c r="B1594" t="s" s="2">
-        <v>3200</v>
+        <v>3205</v>
       </c>
       <c r="C1594" t="s" s="2">
-        <v>3201</v>
+        <v>3206</v>
       </c>
       <c r="D1594" s="2"/>
     </row>
@@ -29328,10 +29814,10 @@
         <v>40</v>
       </c>
       <c r="B1595" t="s" s="2">
-        <v>3202</v>
+        <v>3207</v>
       </c>
       <c r="C1595" t="s" s="2">
-        <v>3203</v>
+        <v>3208</v>
       </c>
       <c r="D1595" s="2"/>
     </row>
@@ -29340,10 +29826,10 @@
         <v>40</v>
       </c>
       <c r="B1596" t="s" s="2">
-        <v>3204</v>
+        <v>3209</v>
       </c>
       <c r="C1596" t="s" s="2">
-        <v>3205</v>
+        <v>3210</v>
       </c>
       <c r="D1596" s="2"/>
     </row>
@@ -29352,10 +29838,10 @@
         <v>40</v>
       </c>
       <c r="B1597" t="s" s="2">
-        <v>3206</v>
+        <v>3211</v>
       </c>
       <c r="C1597" t="s" s="2">
-        <v>3207</v>
+        <v>3212</v>
       </c>
       <c r="D1597" s="2"/>
     </row>
@@ -29364,10 +29850,10 @@
         <v>40</v>
       </c>
       <c r="B1598" t="s" s="2">
-        <v>3208</v>
+        <v>3213</v>
       </c>
       <c r="C1598" t="s" s="2">
-        <v>3209</v>
+        <v>3214</v>
       </c>
       <c r="D1598" s="2"/>
     </row>
@@ -29376,10 +29862,10 @@
         <v>40</v>
       </c>
       <c r="B1599" t="s" s="2">
-        <v>3210</v>
+        <v>3215</v>
       </c>
       <c r="C1599" t="s" s="2">
-        <v>3211</v>
+        <v>3216</v>
       </c>
       <c r="D1599" s="2"/>
     </row>
@@ -29388,10 +29874,10 @@
         <v>40</v>
       </c>
       <c r="B1600" t="s" s="2">
-        <v>3212</v>
+        <v>3217</v>
       </c>
       <c r="C1600" t="s" s="2">
-        <v>3213</v>
+        <v>3218</v>
       </c>
       <c r="D1600" s="2"/>
     </row>
@@ -29400,10 +29886,10 @@
         <v>40</v>
       </c>
       <c r="B1601" t="s" s="2">
-        <v>3214</v>
+        <v>3219</v>
       </c>
       <c r="C1601" t="s" s="2">
-        <v>3215</v>
+        <v>3220</v>
       </c>
       <c r="D1601" s="2"/>
     </row>
@@ -29412,10 +29898,10 @@
         <v>40</v>
       </c>
       <c r="B1602" t="s" s="2">
-        <v>3216</v>
+        <v>3221</v>
       </c>
       <c r="C1602" t="s" s="2">
-        <v>3217</v>
+        <v>3222</v>
       </c>
       <c r="D1602" s="2"/>
     </row>
@@ -29424,10 +29910,10 @@
         <v>40</v>
       </c>
       <c r="B1603" t="s" s="2">
-        <v>3218</v>
+        <v>3223</v>
       </c>
       <c r="C1603" t="s" s="2">
-        <v>3219</v>
+        <v>3224</v>
       </c>
       <c r="D1603" s="2"/>
     </row>
@@ -29436,10 +29922,10 @@
         <v>40</v>
       </c>
       <c r="B1604" t="s" s="2">
-        <v>3220</v>
+        <v>3225</v>
       </c>
       <c r="C1604" t="s" s="2">
-        <v>3221</v>
+        <v>3226</v>
       </c>
       <c r="D1604" s="2"/>
     </row>
@@ -29448,10 +29934,10 @@
         <v>40</v>
       </c>
       <c r="B1605" t="s" s="2">
-        <v>3222</v>
+        <v>3227</v>
       </c>
       <c r="C1605" t="s" s="2">
-        <v>3223</v>
+        <v>3228</v>
       </c>
       <c r="D1605" s="2"/>
     </row>
@@ -29460,10 +29946,10 @@
         <v>40</v>
       </c>
       <c r="B1606" t="s" s="2">
-        <v>3224</v>
+        <v>3229</v>
       </c>
       <c r="C1606" t="s" s="2">
-        <v>3225</v>
+        <v>3230</v>
       </c>
       <c r="D1606" s="2"/>
     </row>
@@ -29472,10 +29958,10 @@
         <v>40</v>
       </c>
       <c r="B1607" t="s" s="2">
-        <v>3226</v>
+        <v>3231</v>
       </c>
       <c r="C1607" t="s" s="2">
-        <v>3227</v>
+        <v>3232</v>
       </c>
       <c r="D1607" s="2"/>
     </row>
@@ -29484,10 +29970,10 @@
         <v>40</v>
       </c>
       <c r="B1608" t="s" s="2">
-        <v>3228</v>
+        <v>3233</v>
       </c>
       <c r="C1608" t="s" s="2">
-        <v>3229</v>
+        <v>3234</v>
       </c>
       <c r="D1608" s="2"/>
     </row>
@@ -29496,10 +29982,10 @@
         <v>40</v>
       </c>
       <c r="B1609" t="s" s="2">
-        <v>3230</v>
+        <v>3235</v>
       </c>
       <c r="C1609" t="s" s="2">
-        <v>3231</v>
+        <v>3236</v>
       </c>
       <c r="D1609" s="2"/>
     </row>
@@ -29508,10 +29994,10 @@
         <v>40</v>
       </c>
       <c r="B1610" t="s" s="2">
-        <v>3232</v>
+        <v>3237</v>
       </c>
       <c r="C1610" t="s" s="2">
-        <v>3233</v>
+        <v>3238</v>
       </c>
       <c r="D1610" s="2"/>
     </row>
@@ -29520,10 +30006,10 @@
         <v>40</v>
       </c>
       <c r="B1611" t="s" s="2">
-        <v>3234</v>
+        <v>3239</v>
       </c>
       <c r="C1611" t="s" s="2">
-        <v>3235</v>
+        <v>3240</v>
       </c>
       <c r="D1611" s="2"/>
     </row>
@@ -29532,10 +30018,10 @@
         <v>40</v>
       </c>
       <c r="B1612" t="s" s="2">
-        <v>3236</v>
+        <v>3241</v>
       </c>
       <c r="C1612" t="s" s="2">
-        <v>3237</v>
+        <v>3242</v>
       </c>
       <c r="D1612" s="2"/>
     </row>
@@ -29544,10 +30030,10 @@
         <v>40</v>
       </c>
       <c r="B1613" t="s" s="2">
-        <v>3238</v>
+        <v>3243</v>
       </c>
       <c r="C1613" t="s" s="2">
-        <v>3239</v>
+        <v>3244</v>
       </c>
       <c r="D1613" s="2"/>
     </row>
@@ -29556,10 +30042,10 @@
         <v>40</v>
       </c>
       <c r="B1614" t="s" s="2">
-        <v>3240</v>
+        <v>3245</v>
       </c>
       <c r="C1614" t="s" s="2">
-        <v>3241</v>
+        <v>3246</v>
       </c>
       <c r="D1614" s="2"/>
     </row>
@@ -29568,10 +30054,10 @@
         <v>40</v>
       </c>
       <c r="B1615" t="s" s="2">
-        <v>3242</v>
+        <v>3247</v>
       </c>
       <c r="C1615" t="s" s="2">
-        <v>3243</v>
+        <v>3248</v>
       </c>
       <c r="D1615" s="2"/>
     </row>
@@ -29580,10 +30066,10 @@
         <v>40</v>
       </c>
       <c r="B1616" t="s" s="2">
-        <v>3244</v>
+        <v>3249</v>
       </c>
       <c r="C1616" t="s" s="2">
-        <v>3245</v>
+        <v>3250</v>
       </c>
       <c r="D1616" s="2"/>
     </row>
@@ -29592,10 +30078,10 @@
         <v>40</v>
       </c>
       <c r="B1617" t="s" s="2">
-        <v>3246</v>
+        <v>3251</v>
       </c>
       <c r="C1617" t="s" s="2">
-        <v>3247</v>
+        <v>3252</v>
       </c>
       <c r="D1617" s="2"/>
     </row>
@@ -29604,10 +30090,10 @@
         <v>40</v>
       </c>
       <c r="B1618" t="s" s="2">
-        <v>3248</v>
+        <v>3253</v>
       </c>
       <c r="C1618" t="s" s="2">
-        <v>3249</v>
+        <v>3254</v>
       </c>
       <c r="D1618" s="2"/>
     </row>
@@ -29616,10 +30102,10 @@
         <v>40</v>
       </c>
       <c r="B1619" t="s" s="2">
-        <v>3250</v>
+        <v>3255</v>
       </c>
       <c r="C1619" t="s" s="2">
-        <v>3251</v>
+        <v>3256</v>
       </c>
       <c r="D1619" s="2"/>
     </row>
@@ -29628,10 +30114,10 @@
         <v>40</v>
       </c>
       <c r="B1620" t="s" s="2">
-        <v>3252</v>
+        <v>3257</v>
       </c>
       <c r="C1620" t="s" s="2">
-        <v>3253</v>
+        <v>3258</v>
       </c>
       <c r="D1620" s="2"/>
     </row>
@@ -29640,10 +30126,10 @@
         <v>40</v>
       </c>
       <c r="B1621" t="s" s="2">
-        <v>3254</v>
+        <v>3259</v>
       </c>
       <c r="C1621" t="s" s="2">
-        <v>3255</v>
+        <v>3260</v>
       </c>
       <c r="D1621" s="2"/>
     </row>
@@ -29652,10 +30138,10 @@
         <v>40</v>
       </c>
       <c r="B1622" t="s" s="2">
-        <v>3256</v>
+        <v>3261</v>
       </c>
       <c r="C1622" t="s" s="2">
-        <v>3257</v>
+        <v>3262</v>
       </c>
       <c r="D1622" s="2"/>
     </row>
@@ -29664,10 +30150,10 @@
         <v>40</v>
       </c>
       <c r="B1623" t="s" s="2">
-        <v>3258</v>
+        <v>3263</v>
       </c>
       <c r="C1623" t="s" s="2">
-        <v>3259</v>
+        <v>3264</v>
       </c>
       <c r="D1623" s="2"/>
     </row>
@@ -29676,10 +30162,10 @@
         <v>40</v>
       </c>
       <c r="B1624" t="s" s="2">
-        <v>3260</v>
+        <v>3265</v>
       </c>
       <c r="C1624" t="s" s="2">
-        <v>3261</v>
+        <v>3266</v>
       </c>
       <c r="D1624" s="2"/>
     </row>
@@ -29688,10 +30174,10 @@
         <v>40</v>
       </c>
       <c r="B1625" t="s" s="2">
-        <v>3262</v>
+        <v>3267</v>
       </c>
       <c r="C1625" t="s" s="2">
-        <v>3263</v>
+        <v>3268</v>
       </c>
       <c r="D1625" s="2"/>
     </row>
@@ -29700,10 +30186,10 @@
         <v>40</v>
       </c>
       <c r="B1626" t="s" s="2">
-        <v>3264</v>
+        <v>3269</v>
       </c>
       <c r="C1626" t="s" s="2">
-        <v>3265</v>
+        <v>3270</v>
       </c>
       <c r="D1626" s="2"/>
     </row>
@@ -29712,10 +30198,10 @@
         <v>40</v>
       </c>
       <c r="B1627" t="s" s="2">
-        <v>3266</v>
+        <v>3271</v>
       </c>
       <c r="C1627" t="s" s="2">
-        <v>3267</v>
+        <v>3272</v>
       </c>
       <c r="D1627" s="2"/>
     </row>
@@ -29724,10 +30210,10 @@
         <v>40</v>
       </c>
       <c r="B1628" t="s" s="2">
-        <v>3268</v>
+        <v>3273</v>
       </c>
       <c r="C1628" t="s" s="2">
-        <v>3269</v>
+        <v>3274</v>
       </c>
       <c r="D1628" s="2"/>
     </row>
@@ -29736,10 +30222,10 @@
         <v>40</v>
       </c>
       <c r="B1629" t="s" s="2">
-        <v>3270</v>
+        <v>3275</v>
       </c>
       <c r="C1629" t="s" s="2">
-        <v>3271</v>
+        <v>3276</v>
       </c>
       <c r="D1629" s="2"/>
     </row>
@@ -29748,10 +30234,10 @@
         <v>40</v>
       </c>
       <c r="B1630" t="s" s="2">
-        <v>3272</v>
+        <v>3277</v>
       </c>
       <c r="C1630" t="s" s="2">
-        <v>3273</v>
+        <v>3102</v>
       </c>
       <c r="D1630" s="2"/>
     </row>
@@ -29760,10 +30246,10 @@
         <v>40</v>
       </c>
       <c r="B1631" t="s" s="2">
-        <v>3274</v>
+        <v>3278</v>
       </c>
       <c r="C1631" t="s" s="2">
-        <v>3275</v>
+        <v>3279</v>
       </c>
       <c r="D1631" s="2"/>
     </row>
@@ -29772,10 +30258,10 @@
         <v>40</v>
       </c>
       <c r="B1632" t="s" s="2">
-        <v>3276</v>
+        <v>3280</v>
       </c>
       <c r="C1632" t="s" s="2">
-        <v>3277</v>
+        <v>3281</v>
       </c>
       <c r="D1632" s="2"/>
     </row>
@@ -29784,10 +30270,10 @@
         <v>40</v>
       </c>
       <c r="B1633" t="s" s="2">
-        <v>3278</v>
+        <v>3282</v>
       </c>
       <c r="C1633" t="s" s="2">
-        <v>3279</v>
+        <v>3283</v>
       </c>
       <c r="D1633" s="2"/>
     </row>
@@ -29796,10 +30282,10 @@
         <v>40</v>
       </c>
       <c r="B1634" t="s" s="2">
-        <v>3280</v>
+        <v>3284</v>
       </c>
       <c r="C1634" t="s" s="2">
-        <v>3281</v>
+        <v>3285</v>
       </c>
       <c r="D1634" s="2"/>
     </row>
@@ -29808,10 +30294,10 @@
         <v>40</v>
       </c>
       <c r="B1635" t="s" s="2">
-        <v>3282</v>
+        <v>3286</v>
       </c>
       <c r="C1635" t="s" s="2">
-        <v>3283</v>
+        <v>3287</v>
       </c>
       <c r="D1635" s="2"/>
     </row>
@@ -29820,10 +30306,10 @@
         <v>40</v>
       </c>
       <c r="B1636" t="s" s="2">
-        <v>3284</v>
+        <v>3288</v>
       </c>
       <c r="C1636" t="s" s="2">
-        <v>3285</v>
+        <v>3289</v>
       </c>
       <c r="D1636" s="2"/>
     </row>
@@ -29832,12 +30318,960 @@
         <v>40</v>
       </c>
       <c r="B1637" t="s" s="2">
-        <v>3286</v>
+        <v>3290</v>
       </c>
       <c r="C1637" t="s" s="2">
-        <v>3287</v>
+        <v>3291</v>
       </c>
       <c r="D1637" s="2"/>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1638" t="s" s="2">
+        <v>3292</v>
+      </c>
+      <c r="C1638" t="s" s="2">
+        <v>3293</v>
+      </c>
+      <c r="D1638" s="2"/>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1639" t="s" s="2">
+        <v>3294</v>
+      </c>
+      <c r="C1639" t="s" s="2">
+        <v>3295</v>
+      </c>
+      <c r="D1639" s="2"/>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1640" t="s" s="2">
+        <v>3296</v>
+      </c>
+      <c r="C1640" t="s" s="2">
+        <v>3297</v>
+      </c>
+      <c r="D1640" s="2"/>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1641" t="s" s="2">
+        <v>3298</v>
+      </c>
+      <c r="C1641" t="s" s="2">
+        <v>3299</v>
+      </c>
+      <c r="D1641" s="2"/>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1642" t="s" s="2">
+        <v>3300</v>
+      </c>
+      <c r="C1642" t="s" s="2">
+        <v>3301</v>
+      </c>
+      <c r="D1642" s="2"/>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1643" t="s" s="2">
+        <v>3302</v>
+      </c>
+      <c r="C1643" t="s" s="2">
+        <v>3303</v>
+      </c>
+      <c r="D1643" s="2"/>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1644" t="s" s="2">
+        <v>3304</v>
+      </c>
+      <c r="C1644" t="s" s="2">
+        <v>3305</v>
+      </c>
+      <c r="D1644" s="2"/>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1645" t="s" s="2">
+        <v>3306</v>
+      </c>
+      <c r="C1645" t="s" s="2">
+        <v>3307</v>
+      </c>
+      <c r="D1645" s="2"/>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1646" t="s" s="2">
+        <v>3308</v>
+      </c>
+      <c r="C1646" t="s" s="2">
+        <v>3309</v>
+      </c>
+      <c r="D1646" s="2"/>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1647" t="s" s="2">
+        <v>3310</v>
+      </c>
+      <c r="C1647" t="s" s="2">
+        <v>3311</v>
+      </c>
+      <c r="D1647" s="2"/>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1648" t="s" s="2">
+        <v>3312</v>
+      </c>
+      <c r="C1648" t="s" s="2">
+        <v>3313</v>
+      </c>
+      <c r="D1648" s="2"/>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1649" t="s" s="2">
+        <v>3314</v>
+      </c>
+      <c r="C1649" t="s" s="2">
+        <v>3315</v>
+      </c>
+      <c r="D1649" s="2"/>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1650" t="s" s="2">
+        <v>3316</v>
+      </c>
+      <c r="C1650" t="s" s="2">
+        <v>3317</v>
+      </c>
+      <c r="D1650" s="2"/>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1651" t="s" s="2">
+        <v>3318</v>
+      </c>
+      <c r="C1651" t="s" s="2">
+        <v>3319</v>
+      </c>
+      <c r="D1651" s="2"/>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1652" t="s" s="2">
+        <v>3320</v>
+      </c>
+      <c r="C1652" t="s" s="2">
+        <v>3321</v>
+      </c>
+      <c r="D1652" s="2"/>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1653" t="s" s="2">
+        <v>3322</v>
+      </c>
+      <c r="C1653" t="s" s="2">
+        <v>3323</v>
+      </c>
+      <c r="D1653" s="2"/>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1654" t="s" s="2">
+        <v>3324</v>
+      </c>
+      <c r="C1654" t="s" s="2">
+        <v>3325</v>
+      </c>
+      <c r="D1654" s="2"/>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1655" t="s" s="2">
+        <v>3326</v>
+      </c>
+      <c r="C1655" t="s" s="2">
+        <v>3327</v>
+      </c>
+      <c r="D1655" s="2"/>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1656" t="s" s="2">
+        <v>3328</v>
+      </c>
+      <c r="C1656" t="s" s="2">
+        <v>3329</v>
+      </c>
+      <c r="D1656" s="2"/>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1657" t="s" s="2">
+        <v>3330</v>
+      </c>
+      <c r="C1657" t="s" s="2">
+        <v>3331</v>
+      </c>
+      <c r="D1657" s="2"/>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1658" t="s" s="2">
+        <v>3332</v>
+      </c>
+      <c r="C1658" t="s" s="2">
+        <v>3333</v>
+      </c>
+      <c r="D1658" s="2"/>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1659" t="s" s="2">
+        <v>3334</v>
+      </c>
+      <c r="C1659" t="s" s="2">
+        <v>3335</v>
+      </c>
+      <c r="D1659" s="2"/>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1660" t="s" s="2">
+        <v>3336</v>
+      </c>
+      <c r="C1660" t="s" s="2">
+        <v>3337</v>
+      </c>
+      <c r="D1660" s="2"/>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1661" t="s" s="2">
+        <v>3338</v>
+      </c>
+      <c r="C1661" t="s" s="2">
+        <v>3339</v>
+      </c>
+      <c r="D1661" s="2"/>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1662" t="s" s="2">
+        <v>3340</v>
+      </c>
+      <c r="C1662" t="s" s="2">
+        <v>3341</v>
+      </c>
+      <c r="D1662" s="2"/>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1663" t="s" s="2">
+        <v>3342</v>
+      </c>
+      <c r="C1663" t="s" s="2">
+        <v>3343</v>
+      </c>
+      <c r="D1663" s="2"/>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1664" t="s" s="2">
+        <v>3344</v>
+      </c>
+      <c r="C1664" t="s" s="2">
+        <v>3345</v>
+      </c>
+      <c r="D1664" s="2"/>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1665" t="s" s="2">
+        <v>3346</v>
+      </c>
+      <c r="C1665" t="s" s="2">
+        <v>3347</v>
+      </c>
+      <c r="D1665" s="2"/>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1666" t="s" s="2">
+        <v>3348</v>
+      </c>
+      <c r="C1666" t="s" s="2">
+        <v>3349</v>
+      </c>
+      <c r="D1666" s="2"/>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1667" t="s" s="2">
+        <v>3350</v>
+      </c>
+      <c r="C1667" t="s" s="2">
+        <v>3351</v>
+      </c>
+      <c r="D1667" s="2"/>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1668" t="s" s="2">
+        <v>3352</v>
+      </c>
+      <c r="C1668" t="s" s="2">
+        <v>3353</v>
+      </c>
+      <c r="D1668" s="2"/>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1669" t="s" s="2">
+        <v>3354</v>
+      </c>
+      <c r="C1669" t="s" s="2">
+        <v>3355</v>
+      </c>
+      <c r="D1669" s="2"/>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1670" t="s" s="2">
+        <v>3356</v>
+      </c>
+      <c r="C1670" t="s" s="2">
+        <v>3357</v>
+      </c>
+      <c r="D1670" s="2"/>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1671" t="s" s="2">
+        <v>3358</v>
+      </c>
+      <c r="C1671" t="s" s="2">
+        <v>3359</v>
+      </c>
+      <c r="D1671" s="2"/>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1672" t="s" s="2">
+        <v>3360</v>
+      </c>
+      <c r="C1672" t="s" s="2">
+        <v>3361</v>
+      </c>
+      <c r="D1672" s="2"/>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1673" t="s" s="2">
+        <v>3362</v>
+      </c>
+      <c r="C1673" t="s" s="2">
+        <v>3363</v>
+      </c>
+      <c r="D1673" s="2"/>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1674" t="s" s="2">
+        <v>3364</v>
+      </c>
+      <c r="C1674" t="s" s="2">
+        <v>3365</v>
+      </c>
+      <c r="D1674" s="2"/>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1675" t="s" s="2">
+        <v>3366</v>
+      </c>
+      <c r="C1675" t="s" s="2">
+        <v>3367</v>
+      </c>
+      <c r="D1675" s="2"/>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1676" t="s" s="2">
+        <v>3368</v>
+      </c>
+      <c r="C1676" t="s" s="2">
+        <v>3369</v>
+      </c>
+      <c r="D1676" s="2"/>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1677" t="s" s="2">
+        <v>3370</v>
+      </c>
+      <c r="C1677" t="s" s="2">
+        <v>3371</v>
+      </c>
+      <c r="D1677" s="2"/>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1678" t="s" s="2">
+        <v>3372</v>
+      </c>
+      <c r="C1678" t="s" s="2">
+        <v>3373</v>
+      </c>
+      <c r="D1678" s="2"/>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1679" t="s" s="2">
+        <v>3374</v>
+      </c>
+      <c r="C1679" t="s" s="2">
+        <v>3375</v>
+      </c>
+      <c r="D1679" s="2"/>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1680" t="s" s="2">
+        <v>3376</v>
+      </c>
+      <c r="C1680" t="s" s="2">
+        <v>3377</v>
+      </c>
+      <c r="D1680" s="2"/>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1681" t="s" s="2">
+        <v>3378</v>
+      </c>
+      <c r="C1681" t="s" s="2">
+        <v>3379</v>
+      </c>
+      <c r="D1681" s="2"/>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1682" t="s" s="2">
+        <v>3380</v>
+      </c>
+      <c r="C1682" t="s" s="2">
+        <v>3381</v>
+      </c>
+      <c r="D1682" s="2"/>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1683" t="s" s="2">
+        <v>3382</v>
+      </c>
+      <c r="C1683" t="s" s="2">
+        <v>3383</v>
+      </c>
+      <c r="D1683" s="2"/>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1684" t="s" s="2">
+        <v>3384</v>
+      </c>
+      <c r="C1684" t="s" s="2">
+        <v>3385</v>
+      </c>
+      <c r="D1684" s="2"/>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1685" t="s" s="2">
+        <v>3386</v>
+      </c>
+      <c r="C1685" t="s" s="2">
+        <v>3387</v>
+      </c>
+      <c r="D1685" s="2"/>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1686" t="s" s="2">
+        <v>3388</v>
+      </c>
+      <c r="C1686" t="s" s="2">
+        <v>3389</v>
+      </c>
+      <c r="D1686" s="2"/>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1687" t="s" s="2">
+        <v>3390</v>
+      </c>
+      <c r="C1687" t="s" s="2">
+        <v>3391</v>
+      </c>
+      <c r="D1687" s="2"/>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1688" t="s" s="2">
+        <v>3392</v>
+      </c>
+      <c r="C1688" t="s" s="2">
+        <v>3393</v>
+      </c>
+      <c r="D1688" s="2"/>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1689" t="s" s="2">
+        <v>3394</v>
+      </c>
+      <c r="C1689" t="s" s="2">
+        <v>3395</v>
+      </c>
+      <c r="D1689" s="2"/>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1690" t="s" s="2">
+        <v>3396</v>
+      </c>
+      <c r="C1690" t="s" s="2">
+        <v>3397</v>
+      </c>
+      <c r="D1690" s="2"/>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1691" t="s" s="2">
+        <v>3398</v>
+      </c>
+      <c r="C1691" t="s" s="2">
+        <v>3399</v>
+      </c>
+      <c r="D1691" s="2"/>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1692" t="s" s="2">
+        <v>3400</v>
+      </c>
+      <c r="C1692" t="s" s="2">
+        <v>3401</v>
+      </c>
+      <c r="D1692" s="2"/>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1693" t="s" s="2">
+        <v>3402</v>
+      </c>
+      <c r="C1693" t="s" s="2">
+        <v>3403</v>
+      </c>
+      <c r="D1693" s="2"/>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1694" t="s" s="2">
+        <v>3404</v>
+      </c>
+      <c r="C1694" t="s" s="2">
+        <v>3405</v>
+      </c>
+      <c r="D1694" s="2"/>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1695" t="s" s="2">
+        <v>3406</v>
+      </c>
+      <c r="C1695" t="s" s="2">
+        <v>3407</v>
+      </c>
+      <c r="D1695" s="2"/>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1696" t="s" s="2">
+        <v>3408</v>
+      </c>
+      <c r="C1696" t="s" s="2">
+        <v>3409</v>
+      </c>
+      <c r="D1696" s="2"/>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1697" t="s" s="2">
+        <v>3410</v>
+      </c>
+      <c r="C1697" t="s" s="2">
+        <v>3411</v>
+      </c>
+      <c r="D1697" s="2"/>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1698" t="s" s="2">
+        <v>3412</v>
+      </c>
+      <c r="C1698" t="s" s="2">
+        <v>3413</v>
+      </c>
+      <c r="D1698" s="2"/>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1699" t="s" s="2">
+        <v>3414</v>
+      </c>
+      <c r="C1699" t="s" s="2">
+        <v>3415</v>
+      </c>
+      <c r="D1699" s="2"/>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1700" t="s" s="2">
+        <v>3416</v>
+      </c>
+      <c r="C1700" t="s" s="2">
+        <v>3417</v>
+      </c>
+      <c r="D1700" s="2"/>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1701" t="s" s="2">
+        <v>3418</v>
+      </c>
+      <c r="C1701" t="s" s="2">
+        <v>3419</v>
+      </c>
+      <c r="D1701" s="2"/>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1702" t="s" s="2">
+        <v>3420</v>
+      </c>
+      <c r="C1702" t="s" s="2">
+        <v>3421</v>
+      </c>
+      <c r="D1702" s="2"/>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1703" t="s" s="2">
+        <v>3422</v>
+      </c>
+      <c r="C1703" t="s" s="2">
+        <v>3423</v>
+      </c>
+      <c r="D1703" s="2"/>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1704" t="s" s="2">
+        <v>3424</v>
+      </c>
+      <c r="C1704" t="s" s="2">
+        <v>3425</v>
+      </c>
+      <c r="D1704" s="2"/>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1705" t="s" s="2">
+        <v>3426</v>
+      </c>
+      <c r="C1705" t="s" s="2">
+        <v>3427</v>
+      </c>
+      <c r="D1705" s="2"/>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1706" t="s" s="2">
+        <v>3428</v>
+      </c>
+      <c r="C1706" t="s" s="2">
+        <v>3429</v>
+      </c>
+      <c r="D1706" s="2"/>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1707" t="s" s="2">
+        <v>3430</v>
+      </c>
+      <c r="C1707" t="s" s="2">
+        <v>3431</v>
+      </c>
+      <c r="D1707" s="2"/>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1708" t="s" s="2">
+        <v>3432</v>
+      </c>
+      <c r="C1708" t="s" s="2">
+        <v>3433</v>
+      </c>
+      <c r="D1708" s="2"/>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1709" t="s" s="2">
+        <v>3434</v>
+      </c>
+      <c r="C1709" t="s" s="2">
+        <v>3435</v>
+      </c>
+      <c r="D1709" s="2"/>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1710" t="s" s="2">
+        <v>3436</v>
+      </c>
+      <c r="C1710" t="s" s="2">
+        <v>3437</v>
+      </c>
+      <c r="D1710" s="2"/>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1711" t="s" s="2">
+        <v>3438</v>
+      </c>
+      <c r="C1711" t="s" s="2">
+        <v>3439</v>
+      </c>
+      <c r="D1711" s="2"/>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1712" t="s" s="2">
+        <v>3440</v>
+      </c>
+      <c r="C1712" t="s" s="2">
+        <v>3441</v>
+      </c>
+      <c r="D1712" s="2"/>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1713" t="s" s="2">
+        <v>3442</v>
+      </c>
+      <c r="C1713" t="s" s="2">
+        <v>3443</v>
+      </c>
+      <c r="D1713" s="2"/>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1714" t="s" s="2">
+        <v>3444</v>
+      </c>
+      <c r="C1714" t="s" s="2">
+        <v>3445</v>
+      </c>
+      <c r="D1714" s="2"/>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1715" t="s" s="2">
+        <v>3446</v>
+      </c>
+      <c r="C1715" t="s" s="2">
+        <v>3447</v>
+      </c>
+      <c r="D1715" s="2"/>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B1716" t="s" s="2">
+        <v>3448</v>
+      </c>
+      <c r="C1716" t="s" s="2">
+        <v>3449</v>
+      </c>
+      <c r="D1716" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
